--- a/driving-alert-workproducts/excel/2-2_Project_Result 복사본.xlsx
+++ b/driving-alert-workproducts/excel/2-2_Project_Result 복사본.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juns/Downloads/중간보고서/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juns/code/work/mobis/PBL/driving-alert-workproducts/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32435AA6-65CD-D949-8DB2-90A9AC759245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4268E75-AA8F-DB4B-90C6-757298C9FE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18480" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18480" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Project_Overview" sheetId="17" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7088" uniqueCount="2717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7268" uniqueCount="2772">
   <si>
     <t>구분</t>
   </si>
@@ -5771,9 +5771,6 @@
     <t>주변 객체와 센서 상태를 반영하여 위험 경고를 판단</t>
   </si>
   <si>
-    <t>Planned</t>
-  </si>
-  <si>
     <t>운전자 상태와 차량 맥락을 반영하여 경고 표시와 안내를 보정</t>
   </si>
   <si>
@@ -5900,73 +5897,19 @@
     <t>차량 서비스 ECU 상태 정보를 입력</t>
   </si>
   <si>
-    <t>보안 게이트웨이 상태를 입력</t>
-  </si>
-  <si>
-    <t>진단 제어 상태를 입력</t>
-  </si>
-  <si>
     <t>충전 ECU 상태 정보를 입력</t>
   </si>
   <si>
-    <t>전력 변환 ECU 상태 정보를 입력</t>
-  </si>
-  <si>
     <t>모터 제어 ECU 상태 정보를 입력</t>
   </si>
   <si>
     <t>인버터 상태를 입력</t>
   </si>
   <si>
-    <t>Req_001,Req_002,Req_003,Req_004,Req_005,Req_006,Req_007,Req_008,Req_009,Req_010,Req_011,Req_012</t>
-  </si>
-  <si>
-    <t>입력 변화 후 150ms 이내 기본 경고와 구간 정보가 정상 반영되고 통신 누락이 없다</t>
-  </si>
-  <si>
-    <t>긴급 알림 미수신 시 안전 해제와 복귀 통합 검증</t>
-  </si>
-  <si>
-    <t>1000ms 동안 갱신이 없으면 경고가 안전하게 해제되고 150ms 이내 기본 상태로 복귀하며 중복 토글이 없다</t>
-  </si>
-  <si>
     <t>긴급차량 근접 위험도 기반 감속 보조 요청과 경고 출력 통합 검증</t>
   </si>
   <si>
-    <t>객체 입력은 100ms 이내 반영되고 위험 경고는 150ms 이내 발생하며 신뢰도 저하 시 강등과 이벤트 기록이 누락 없이 수행된다</t>
-  </si>
-  <si>
-    <t>엔진, 변속, 동력 상태 통합 검증</t>
-  </si>
-  <si>
-    <t>엔진, 변속, 동력 상태가 100ms 주기로 일관되게 반영된다</t>
-  </si>
-  <si>
-    <t>가감속, 조향, 제동, 차체 상태 통합 검증</t>
-  </si>
-  <si>
-    <t>입력과 차체 상태 정보가 100ms 기준으로 일관되게 반영된다</t>
-  </si>
-  <si>
-    <t>비상등, 창문, 차체 편의 상태 통합 검증</t>
-  </si>
-  <si>
-    <t>차체 제어 상태가 일관되게 유지된다</t>
-  </si>
-  <si>
     <t>표시 상태와 연계 이벤트가 50/100ms 규칙을 만족한다</t>
-  </si>
-  <si>
-    <t>공조, 시트, 미러, 도어, 와이퍼, 보안 상태 통합 검증</t>
-  </si>
-  <si>
-    <t>관련 상태와 제어 정보가 100ms 주기로 연계되고 150ms 이내 정책에 반영된다</t>
-  </si>
-  <si>
-    <t>오디오, 음성 안내, TTS 상태 통합 검증</t>
-  </si>
-  <si>
-    <t>오디오와 음성 상태가 50/100ms 규칙을 만족하고 150ms 이내 HMI 정책에 반영된다</t>
   </si>
   <si>
     <t>EPB, EHB, VSM, ECS, CDC 상태 통합 검증</t>
@@ -6777,33 +6720,18 @@
     <t>ST_003</t>
   </si>
   <si>
-    <t>일반 구간에서 제한속도 초과 시 경고가 활성되는지 확인한다.</t>
-  </si>
-  <si>
     <t>ST_004</t>
   </si>
   <si>
-    <t>일반 구간에서 감속 후 과속 조건이 해제되면 경고가 정상 해제되는지 확인한다.</t>
-  </si>
-  <si>
     <t>ST_005</t>
   </si>
   <si>
-    <t>일반 구간에서 스쿨존으로 진입할 때 구간 정책이 즉시 전환되는지 확인한다.</t>
-  </si>
-  <si>
     <t>ST_006</t>
   </si>
   <si>
-    <t>스쿨존 이탈 후 일반 구간 기준으로 정상 복귀되는지 확인한다.</t>
-  </si>
-  <si>
     <t>ST_007</t>
   </si>
   <si>
-    <t>일반 구간에서 고속 구간으로 전환될 때 경고 정책이 즉시 반영되는지 확인한다.</t>
-  </si>
-  <si>
     <t>ST_008</t>
   </si>
   <si>
@@ -6819,9 +6747,6 @@
     <t>ST_010</t>
   </si>
   <si>
-    <t>유도 구간에서 우회전 안내가 들어오면 우측 방향 정보와 경고 안내가 일관되게 표시되고 종료 후 기본 상태로 복귀되는지 확인한다.</t>
-  </si>
-  <si>
     <t>ST_011</t>
   </si>
   <si>
@@ -6867,9 +6792,6 @@
     <t>ST_018</t>
   </si>
   <si>
-    <t>경찰 또는 구급 긴급 이벤트 발생 시 Ethernet 경로의 외부 송신 메시지가 정의된 100ms 주기로 연속 관찰되는지 확인한다.</t>
-  </si>
-  <si>
     <t>ST_019</t>
   </si>
   <si>
@@ -6885,15 +6807,9 @@
     <t>ST_021</t>
   </si>
   <si>
-    <t>교차로에서 긴급차량 접근과 TTC 충돌 위험이 함께 높아질 때 자동 감속 보조 요청과 경고 출력이 함께 활성되는지 확인한다. (SIL Scenario 15/16/17/19)</t>
-  </si>
-  <si>
     <t>ST_022</t>
   </si>
   <si>
-    <t>합류 구간에서 긴급차량 접근과 TTC 충돌 위험이 함께 높아질 때 자동 감속 보조 요청과 경고 출력이 함께 활성되는지 확인한다. (SIL Scenario 15/16/17/19)</t>
-  </si>
-  <si>
     <t>ST_023</t>
   </si>
   <si>
@@ -6915,51 +6831,27 @@
     <t>ST_026</t>
   </si>
   <si>
-    <t>전방 객체 급접근이 발생할 때 위험 경고와 이벤트 기록이 일관되게 동작하는지 확인한다. (Pre-Activation)</t>
-  </si>
-  <si>
     <t>ST_027</t>
   </si>
   <si>
-    <t>교차로 측방 접근이 발생할 때 위험 경고와 이벤트 기록이 일관되게 동작하는지 확인한다. (Pre-Activation)</t>
-  </si>
-  <si>
     <t>ST_028</t>
   </si>
   <si>
-    <t>합류 또는 끼어들기 위험이 발생할 때 위험 경고와 이벤트 기록이 일관되게 동작하는지 확인한다. (Pre-Activation)</t>
-  </si>
-  <si>
     <t>ST_029</t>
   </si>
   <si>
-    <t>방향지시등, 주행모드, 안전벨트, 접근거리 표시가 함께 반영될 때 경고 안내가 사용자 기대대로 보정되는지 확인한다. (Pre-Activation)</t>
-  </si>
-  <si>
     <t>ST_030</t>
   </si>
   <si>
-    <t>표시 설정과 음량 설정 변경이 경고 안내 정책에 즉시 반영되는지 확인한다. (Pre-Activation)</t>
-  </si>
-  <si>
     <t>ST_031</t>
   </si>
   <si>
-    <t>경고 발생 후 이력 조회를 수행할 때 최근 경고 순서와 원인 정보가 사용자 화면에 일관되게 제공되는지 확인한다. (Pre-Activation)</t>
-  </si>
-  <si>
     <t>ST_032</t>
   </si>
   <si>
-    <t>입력 지연과 상태 전이가 발생해도 경고 안내가 안정적으로 유지되는지 확인한다. (Pre-Activation)</t>
-  </si>
-  <si>
     <t>ST_033</t>
   </si>
   <si>
-    <t>채널 전환과 오디오 경합이 발생해도 경고 안내가 안정적으로 유지되는지 확인한다. (Pre-Activation)</t>
-  </si>
-  <si>
     <t>ST_034</t>
   </si>
   <si>
@@ -6987,9 +6879,6 @@
     <t>ST_038</t>
   </si>
   <si>
-    <t>차량 서비스, 보안, 진단 상태 변화가 시스템 시나리오에서 경고 정보 전달 가용성과 fail-safe 정책에 일관되게 반영되는지 확인한다.</t>
-  </si>
-  <si>
     <t>ST_039</t>
   </si>
   <si>
@@ -7011,9 +6900,6 @@
     <t>IT_001</t>
   </si>
   <si>
-    <t>차량 속도, 조향, 구간 정보 기반 기본 경고 판단 통합 검증</t>
-  </si>
-  <si>
     <t>IT_002</t>
   </si>
   <si>
@@ -7050,21 +6936,9 @@
     <t>IT_005</t>
   </si>
   <si>
-    <t>Req_005,Req_008,Req_009,Req_013,Req_014,Req_015,Req_016,Req_019,Req_020,Req_021,Req_026,Req_033,Req_034,Req_035,Req_036</t>
-  </si>
-  <si>
-    <t>기본 경고 결과의 앰비언트 및 클러스터 출력 통합 검증</t>
-  </si>
-  <si>
-    <t>경고 문구, 색상, 패턴, 복귀 동작이 일치하고 출력 주기 50ms가 유지된다</t>
-  </si>
-  <si>
     <t>IT_006</t>
   </si>
   <si>
-    <t>Req_023,Req_032,Req_033</t>
-  </si>
-  <si>
     <t>IT_007</t>
   </si>
   <si>
@@ -7089,54 +6963,21 @@
     <t>IT_009</t>
   </si>
   <si>
-    <t>Req_057,Req_058,Req_059,Req_060,Req_061,Req_062,Req_063,Req_064,Req_065,Req_066</t>
-  </si>
-  <si>
-    <t>객체 위험 판단 및 이벤트 기록 통합 검증</t>
-  </si>
-  <si>
     <t>IT_010</t>
   </si>
   <si>
-    <t>Req_067,Req_068,Req_069,Req_070,Req_071,Req_072,Req_073,Req_074</t>
-  </si>
-  <si>
-    <t>운전자 상태, 경고 설정, 접근거리 표시 반영 통합 검증</t>
-  </si>
-  <si>
-    <t>입력 보정은 150ms 이내 반영되고 접근거리 표시는 200ms 이내 갱신되며 표시·음량 설정은 150ms 이내 반영된다</t>
-  </si>
-  <si>
     <t>IT_011</t>
   </si>
   <si>
-    <t>Req_049,Req_050,Req_057,Req_058,Req_059,Req_060,Req_061,Req_062,Req_063</t>
-  </si>
-  <si>
-    <t>긴급차량 접근과 교차로/합류 TTC 충돌 위험 동시 입력 통합 검증</t>
-  </si>
-  <si>
-    <t>긴급차량이 교차로 또는 합류 구간에서 접근하고 TTC 충돌 위험이 기준 이상이면 자동 감속 보조 요청이 생성되며 우선 경고 선택과 표시 채널 출력이 상충 없이 유지된다</t>
-  </si>
-  <si>
     <t>IT_012</t>
   </si>
   <si>
-    <t>Req_037,Req_038</t>
-  </si>
-  <si>
     <t>IT_013</t>
   </si>
   <si>
-    <t>Req_039,Req_040,Req_041</t>
-  </si>
-  <si>
     <t>IT_014</t>
   </si>
   <si>
-    <t>Req_042,Req_043</t>
-  </si>
-  <si>
     <t>IT_015</t>
   </si>
   <si>
@@ -7146,9 +6987,6 @@
     <t>IT_016</t>
   </si>
   <si>
-    <t>Req_045,Req_046,Req_047</t>
-  </si>
-  <si>
     <t>IT_017</t>
   </si>
   <si>
@@ -7158,24 +6996,12 @@
     <t>Req_078,Req_079</t>
   </si>
   <si>
-    <t>주요 출력 채널 가용성 및 대체 출력 통합 검증</t>
-  </si>
-  <si>
-    <t>출력 채널 상태 이상이 누락 없이 반영되고 대체 출력 전환 규칙이 150ms 내 충족된다</t>
-  </si>
-  <si>
     <t>IT_019</t>
   </si>
   <si>
-    <t>Req_071,Req_072,Req_073,Req_074</t>
-  </si>
-  <si>
     <t>접근거리 표시와 경고 이력 조회 통합 검증</t>
   </si>
   <si>
-    <t>접근거리 표시가 200ms 이내 갱신되고 경고 이력 조회 요청에 대한 응답이 누락 없이 반영된다</t>
-  </si>
-  <si>
     <t>IT_020</t>
   </si>
   <si>
@@ -7215,51 +7041,21 @@
     <t>차량 서비스, 보안, 진단 상태 통합 검증</t>
   </si>
   <si>
-    <t>IBOX, SGW, DCM 관련 서비스 상태가 100ms 주기로 반영되고 경고 정보 전달 가용성과 서비스 강등 상태가 즉시 반영된다</t>
-  </si>
-  <si>
     <t>IT_025</t>
   </si>
   <si>
     <t>Req_094,Req_095</t>
   </si>
   <si>
-    <t>충전, 전력 변환, 구동 상태 통합 검증</t>
-  </si>
-  <si>
-    <t>OBC, DCDC, MCU, INVERTER 상태가 100ms 주기로 반영되고 150ms 이내 구동 준비와 서비스 경고 맥락에 반영된다</t>
-  </si>
-  <si>
     <t>IT_026</t>
   </si>
   <si>
-    <t>Req_067,Req_068,Req_069,Req_070,Req_071,Req_072,Req_073,Req_074,Req_088,Req_089</t>
-  </si>
-  <si>
-    <t>표시 채널 출력 통합 검증</t>
-  </si>
-  <si>
-    <t>경고 문구, 접근거리, 팝업, 테마, HUD 표시가 각 표시 채널에 일관되게 반영되고 채널 간 출력 차이는 50ms 이내이다</t>
-  </si>
-  <si>
     <t>IT_027</t>
   </si>
   <si>
-    <t>Req_044,Req_067,Req_068,Req_069,Req_070,Req_071,Req_072,Req_073,Req_074,Req_075,Req_076,Req_077,Req_078,Req_079,Req_080,Req_081,Req_082,Req_088,Req_089</t>
-  </si>
-  <si>
-    <t>오디오 안내 출력 통합 검증</t>
-  </si>
-  <si>
-    <t>오디오 포커스, 음량, 음성안내, TTS 상태가 일관되게 반영되고 경합 시 150ms 이내 안내 정책이 안정화된다</t>
-  </si>
-  <si>
     <t>IT_028</t>
   </si>
   <si>
-    <t>Req_120</t>
-  </si>
-  <si>
     <t>경찰 긴급 알림 송신 경로 통합 검증</t>
   </si>
   <si>
@@ -7269,9 +7065,6 @@
     <t>IT_029</t>
   </si>
   <si>
-    <t>Req_121</t>
-  </si>
-  <si>
     <t>구급 긴급 알림 송신 경로 통합 검증</t>
   </si>
   <si>
@@ -7291,15 +7084,6 @@
   </si>
   <si>
     <t>UT_005 - ADAS (WARN_ARB_MGR, V2 확장)</t>
-  </si>
-  <si>
-    <t>UT_006 - ADAS (ADAS_WARN_CTRL, ADAS 객체 확장, Planned)</t>
-  </si>
-  <si>
-    <t>UT_007 - CLU (CLU_HMI_CTRL, 차량 경보 편의 확장, Planned)</t>
-  </si>
-  <si>
-    <t>UT_008 - CGW (DOMAIN_BOUNDARY_MGR, 경고 강건성·인지성 확장, Planned)</t>
   </si>
   <si>
     <t>UT_009 - IVI (NAV_CTX_MGR)</t>
@@ -9249,6 +9033,387 @@
   <si>
     <t>의미</t>
     <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>UT_006 - ADAS (ADAS_WARN_CTRL, ADAS 객체 확장)</t>
+  </si>
+  <si>
+    <t>UT_007 - CLU (CLU_HMI_CTRL, 차량 경보 편의 확장)</t>
+  </si>
+  <si>
+    <t>UT_008 - CGW (DOMAIN_BOUNDARY_MGR, 경고 강건성·인지성 확장)</t>
+  </si>
+  <si>
+    <t>보안 게이트웨이 상태를 입력하여 진단 보안 상태와 경로 소유 해석에 반영</t>
+  </si>
+  <si>
+    <t>진단 제어 상태를 입력하여 진단 요청/응답 요약과 서비스 판단 상태에 반영</t>
+  </si>
+  <si>
+    <t>전력 변환 ECU 상태를 입력</t>
+  </si>
+  <si>
+    <t>Req_001,Req_002,Req_003,Req_004,Req_005,Req_006</t>
+  </si>
+  <si>
+    <t>주행 상태 변화에 따른 기본 경고 활성, 비활성, 해제 동작 통합 검증</t>
+  </si>
+  <si>
+    <t>주행 상태에서만 경고 기능이 활성 경로로 진입하고 조건 해제 시 정상 상태로 복귀하며 동일 조건 반복 경고가 억제된다</t>
+  </si>
+  <si>
+    <t>Req_007,Req_008,Req_009,Req_010</t>
+  </si>
+  <si>
+    <t>구간 정보와 제한속도 변화에 따른 기본 및 스쿨존 경고 판단 통합 검증</t>
+  </si>
+  <si>
+    <t>구간, 방향, 거리, 제한속도 정보가 정상 반영되고 스쿨존 및 제한속도 초과 조건이 150ms 이내 경고 판단에 반영된다</t>
+  </si>
+  <si>
+    <t>Req_011,Req_012</t>
+  </si>
+  <si>
+    <t>고속 구간 무조향 조건과 조향 입력 복귀에 따른 경고 통합 검증</t>
+  </si>
+  <si>
+    <t>무조향 조건 지속 시 경고가 발생하고 조향 입력 복귀 시 150ms 이내 정상 해제된다</t>
+  </si>
+  <si>
+    <t>Req_008,Req_009,Req_013,Req_014,Req_015,Req_016,Req_021,Req_026,Req_033,Req_034,Req_035</t>
+  </si>
+  <si>
+    <t>기본 경고 및 긴급 경고 결과의 앰비언트 출력 통합 검증</t>
+  </si>
+  <si>
+    <t>경고 상태에 따른 앰비언트 색상, 패턴, 전환 동작이 일치하고 출력 주기 50ms가 유지된다</t>
+  </si>
+  <si>
+    <t>Req_005,Req_018,Req_019,Req_020,Req_021,Req_026,Req_036</t>
+  </si>
+  <si>
+    <t>기본 경고 및 긴급 경고 결과의 클러스터 안내 출력 통합 검증</t>
+  </si>
+  <si>
+    <t>경고 문구, 긴급차량 종류, 방향 정보가 클러스터 안내와 일치하고 경고 전환 시 반복 토글 없이 안정적으로 표시된다</t>
+  </si>
+  <si>
+    <t>Req_022,Req_023,Req_025,Req_032,Req_076,Req_077</t>
+  </si>
+  <si>
+    <t>긴급 종료 신호 및 미수신 시 안전 해제와 복귀 통합 검증</t>
+  </si>
+  <si>
+    <t>종료 신호 수신 또는 1000ms 동안 갱신이 없으면 stale 보호 정책이 적용되고 경고가 안전하게 해제되며 직전 유효 구간 경고 또는 기본 상태로 150ms 이내 복귀하고 중복 표시와 반복 토글이 없다</t>
+  </si>
+  <si>
+    <t>Req_057,Req_058,Req_059,Req_060,Req_061,Req_062,Req_063,Req_064,Req_065,Req_075</t>
+  </si>
+  <si>
+    <t>객체 위험 판단, 입력 유효성 필터링 및 이벤트 기록 통합 검증</t>
+  </si>
+  <si>
+    <t>객체 입력은 100ms 이내 반영되고 유효성 미달 입력은 경고 판정에서 제외되며 위험 경고는 150ms 이내 발생하고 신뢰도 저하 시 강등과 이벤트 기록이 누락 없이 수행된다</t>
+  </si>
+  <si>
+    <t>안전벨트 상태 기반 경보 강조 반영 통합 검증</t>
+  </si>
+  <si>
+    <t>안전벨트 상태가 경보 강조 수준 결정에 반영되고 경고 등급과 유형이 일관되게 유지된다</t>
+  </si>
+  <si>
+    <t>경보 표시 방식 설정 반영 통합 검증</t>
+  </si>
+  <si>
+    <t>운전자가 선택한 경보 표시 방식이 출력 정책에 반영되고 표시 코드와 방향 정보가 일관되게 유지된다</t>
+  </si>
+  <si>
+    <t>방향지시등 상태 기반 경고 타입 보정 통합 검증</t>
+  </si>
+  <si>
+    <t>방향지시등 상태가 school-zone 경고 타입 보정에 반영되고 우회전 맥락이 일관되게 유지된다</t>
+  </si>
+  <si>
+    <t>주행모드 기반 경보 민감도 반영 통합 검증</t>
+  </si>
+  <si>
+    <t>주행모드와 sport 맥락이 경고 민감도 보정에 반영되고 동일 경고 조건에서 경고 등급이 일관되게 유지된다</t>
+  </si>
+  <si>
+    <t>경보 음량 설정 반영 통합 검증</t>
+  </si>
+  <si>
+    <t>운전자가 선택한 음량 설정이 audio focus, ducking, volume 정책에 반영되고 경고 인지성 상태가 일관되게 유지된다</t>
+  </si>
+  <si>
+    <t>Req_049,Req_050,Req_057,Req_058,Req_059,Req_060,Req_061,Req_062,Req_063,Req_066</t>
+  </si>
+  <si>
+    <t>긴급차량 접근과 교차로/합류 TTC 충돌 위험 동시 입력 시 우선 경고 선택 통합 검증</t>
+  </si>
+  <si>
+    <t>긴급차량이 교차로 또는 합류 구간에서 접근하고 TTC 충돌 위험이 기준 이상이면 자동 감속 보조 요청이 생성되며 최종 경고가 우선순위 규칙에 따라 단일 선택되고 표시 채널 출력이 상충 없이 유지된다</t>
+  </si>
+  <si>
+    <t>정차 및 Park 상태 기준 파워트레인 상태 반영 통합 검증</t>
+  </si>
+  <si>
+    <t>정차 및 Park 상태에서 구동 상태와 속도 정보가 기본 기준선으로 유지되고 불필요한 경고가 발생하지 않는다</t>
+  </si>
+  <si>
+    <t>주행 상태 기준 파워트레인 상태 반영 통합 검증</t>
+  </si>
+  <si>
+    <t>주행 상태에서 구동 상태와 속도 정보가 정상 반영되고 경고 미발생 기준선이 안정적으로 유지된다</t>
+  </si>
+  <si>
+    <t>조향 입력 기준 chassis 상태 반영 통합 검증</t>
+  </si>
+  <si>
+    <t>조향 입력과 차속 정보가 정상 반영되고 조향 기반 경고 판단에 필요한 chassis 상태가 일관되게 유지된다</t>
+  </si>
+  <si>
+    <t>제동 입력 기준 chassis 상태 반영 통합 검증</t>
+  </si>
+  <si>
+    <t>제동 입력과 차속 정보가 정상 반영되고 brake 상태가 감속 보조 및 경고 판단 경로에 일관되게 전달된다</t>
+  </si>
+  <si>
+    <t>가속 입력 기준 chassis 상태 반영 통합 검증</t>
+  </si>
+  <si>
+    <t>가속 입력과 차속 상승이 chassis 주행모드 판단에 반영되고 driveMode와 sport 상태가 일관되게 유지된다</t>
+  </si>
+  <si>
+    <t>비상등 상태 기준 body 반영 통합 검증</t>
+  </si>
+  <si>
+    <t>비상등 On/Off 입력이 상태 변화 없이 누락 없이 반영되고 경고 맥락과 충돌 없이 유지된다</t>
+  </si>
+  <si>
+    <t>창문 상태 기준 body 반영 통합 검증</t>
+  </si>
+  <si>
+    <t>창문 개폐 상태가 door/window 출력 경로에 반영되고 좌우 창문 위치가 일관되게 유지된다</t>
+  </si>
+  <si>
+    <t>실내편의 상태 반영 통합 검증</t>
+  </si>
+  <si>
+    <t>원격 공조와 실내 편의 상태가 차량 상태 표시·제어 정책에 반영되고 전후석 공조와 디지털 접근 맥락이 일관되게 유지된다</t>
+  </si>
+  <si>
+    <t>도어 제어/잠금 상태 반영 통합 검증</t>
+  </si>
+  <si>
+    <t>도어 제어·잠금 상태가 body 제어 출력 경로에 반영되고 도어 잠금/개방 상태가 일관되게 유지된다</t>
+  </si>
+  <si>
+    <t>와이퍼·우적 기본 상태 반영 통합 검증</t>
+  </si>
+  <si>
+    <t>와이퍼·우적 기본 상태가 body 출력 경로에 반영되고 비활성 baseline이 일관되게 유지된다</t>
+  </si>
+  <si>
+    <t>IT_030</t>
+  </si>
+  <si>
+    <t>보안 상태 통합 검증</t>
+  </si>
+  <si>
+    <t>보안 상태가 경고 서비스 경계 상태에 반영되고 진단 상태와 충돌 없이 유지된다</t>
+  </si>
+  <si>
+    <t>IT_031</t>
+  </si>
+  <si>
+    <t>오디오 동시 실행 환경에서 경고 인지성 통합 검증</t>
+  </si>
+  <si>
+    <t>오디오 기능이 동시에 실행되는 상황에서도 경고 인지가 가능하고 관련 상태가 50/100ms 규칙을 만족하며 150ms 이내 HMI 정책에 반영된다</t>
+  </si>
+  <si>
+    <t>IT_032</t>
+  </si>
+  <si>
+    <t>출력 채널 가용성 판정 및 대체 경고 유지 통합 검증</t>
+  </si>
+  <si>
+    <t>출력 채널 가용성이 100ms 이내 갱신 판정되고 주 출력 채널 장애 시 150ms 이내 사용 가능한 대체 채널로 경고가 유지된다</t>
+  </si>
+  <si>
+    <t>IT_033</t>
+  </si>
+  <si>
+    <t>팝업 과밀 억제와 우선 경고 유지 통합 검증</t>
+  </si>
+  <si>
+    <t>복수 경고가 겹치는 상황에서 비긴급 팝업 과밀이 억제되고 우선 경고가 먼저 유지된다</t>
+  </si>
+  <si>
+    <t>IT_034</t>
+  </si>
+  <si>
+    <t>경고 채널 동기 복원 통합 검증</t>
+  </si>
+  <si>
+    <t>채널 불일치 발생 시 동일 경고 맥락으로 복원되고 fail-safe 잔류 없이 일관된 출력 상태가 유지된다</t>
+  </si>
+  <si>
+    <t>IT_035</t>
+  </si>
+  <si>
+    <t>Req_070,Req_071,Req_072</t>
+  </si>
+  <si>
+    <t>접근거리 표시가 200ms 이내 갱신되고 경고 이벤트가 공통 포맷으로 기록되며 경고 이력 조회 요청에 대한 응답이 누락 없이 반영된다</t>
+  </si>
+  <si>
+    <t>IT_036</t>
+  </si>
+  <si>
+    <t>IT_037</t>
+  </si>
+  <si>
+    <t>IT_038</t>
+  </si>
+  <si>
+    <t>IT_039</t>
+  </si>
+  <si>
+    <t>IT_040</t>
+  </si>
+  <si>
+    <t>IBOX, SGW, DCM 관련 서비스 상태가 100ms 주기로 반영되고 경고 정보 전달 가용성과 서비스 fail-safe 상태가 즉시 반영되며 외부 진단기에서 요청/응답 및 보안·서비스 상태가 일관되게 확인된다</t>
+  </si>
+  <si>
+    <t>IT_041</t>
+  </si>
+  <si>
+    <t>충전, 전력 변환, 구동, 변속·열관리 상태 통합 검증</t>
+  </si>
+  <si>
+    <t>OBC, DCDC, MCU, INVERTER와 변속·열관리 관련 상태가 100ms 주기로 반영되고 150ms 이내 구동 준비와 서비스 경고 맥락에 반영된다</t>
+  </si>
+  <si>
+    <t>IT_042</t>
+  </si>
+  <si>
+    <t>Req_067,Req_069,Req_070,Req_073,Req_088,Req_089</t>
+  </si>
+  <si>
+    <t>표시 채널 출력 및 서비스 상태 연계 통합 검증</t>
+  </si>
+  <si>
+    <t>경고 문구와 접근거리 정보가 클러스터/HUD 등 표시 채널에 일관되게 반영되고 표시 방식 설정 및 표시·서비스 상태가 반영되며 채널 간 출력 차이는 50ms 이내이다</t>
+  </si>
+  <si>
+    <t>IT_043</t>
+  </si>
+  <si>
+    <t>Req_048,Req_074,Req_075,Req_076,Req_077,Req_080</t>
+  </si>
+  <si>
+    <t>오디오 안내 인지성과 입력 강건성 통합 검증</t>
+  </si>
+  <si>
+    <t>음량 설정이 반영된 상태에서도 오디오 경합 상황에서 경고 인지가 가능하고 유효하지 않거나 stale한 입력은 판정에서 제외되며 동일 원인 경고 상태의 반복 진동이 억제된다</t>
+  </si>
+  <si>
+    <t>IT_044</t>
+  </si>
+  <si>
+    <t>Req_096</t>
+  </si>
+  <si>
+    <t>IT_045</t>
+  </si>
+  <si>
+    <t>Req_097</t>
+  </si>
+  <si>
+    <t>일반 구간에서 단일 위험 입력이 발생하면 기본 경고가 활성되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>일반 구간에서 기본 경고 조건이 해제되면 경고가 정상 해제되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>일반 구간 주행 중 스쿨존 진입 후 과속 조건이 유효하면 스쿨존 경고 정책으로 즉시 전환되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>스쿨존 과속 경고 상태에서 일반 구간으로 복귀하면 기본 상태로 정상 복귀되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>일반 구간에서 고속 구간으로 전환되면 고속 구간 경고 판단 정책이 즉시 반영되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>유도 구간에서 우회전 안내가 들어오면 우측 방향 정보와 경고 안내가 표시되고 종료 후 기본 상태로 복귀되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>경찰 긴급 이벤트 발생 시 Ethernet 경로의 외부 송신 메시지가 정의된 100ms 주기로 연속 관찰되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>구급 긴급 이벤트 발생 시 Ethernet 경로의 외부 송신 메시지가 정의된 100ms 주기로 연속 관찰되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>교차로에서 긴급차량 접근과 TTC 충돌 위험이 함께 높아질 때 자동 감속 보조 요청과 경고 출력이 함께 활성되는지 확인한다. (SIL Scenario 213)</t>
+  </si>
+  <si>
+    <t>합류 구간에서 긴급차량 접근과 TTC 충돌 위험이 함께 높아질 때 자동 감속 보조 요청과 경고 출력이 함께 활성되는지 확인한다. (SIL Scenario 238)</t>
+  </si>
+  <si>
+    <t>전방 객체 급접근이 발생할 때 위험 경고와 이벤트 기록이 일관되게 동작하는지 확인한다.</t>
+  </si>
+  <si>
+    <t>교차로 측방 접근이 발생할 때 위험 경고와 이벤트 기록이 일관되게 동작하는지 확인한다.</t>
+  </si>
+  <si>
+    <t>합류 또는 끼어들기 위험이 발생할 때 위험 경고와 이벤트 기록이 일관되게 동작하는지 확인한다.</t>
+  </si>
+  <si>
+    <t>안전벨트 및 운전자 상태 변화가 발생할 때 시스템 경고 안내가 맥락에 맞게 보정되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>긴급 접근거리 표시가 경고 안내와 함께 사용자 화면에 일관되게 반영되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>표시 설정과 음량 설정 변경이 경고 안내 정책에 즉시 반영되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>경고 발생 후 이력 조회를 수행할 때 최근 경고 순서와 원인 정보가 사용자 화면에 일관되게 제공되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>짧은 시간 내 동일 경고가 재진입해도 중복 팝업 억제와 경고 안내 안정성이 유지되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>긴급 경고 timeout clear 이후 이전 유효 경고가 불필요한 진동 없이 안정적으로 복원되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>fail-safe 해제 후 경고 경로가 정상 상태로 안정적으로 복귀하는지 확인한다.</t>
+  </si>
+  <si>
+    <t>경고 오디오가 활성화된 상태에서 오디오 집중 채널과 감쇄 정책이 안정적으로 유지되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>시각 우선 경고 모드에서 팝업 우선순위와 클러스터 동기가 안정적으로 유지되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>ST_042</t>
+  </si>
+  <si>
+    <t>ST_043</t>
+  </si>
+  <si>
+    <t>차량 서비스, 보안, 진단 상태 변화가 시스템 시나리오에서 경고 정보 전달 가용성, fail-safe 정책, 외부 진단기 확인 결과에 일관되게 반영되는지 확인한다.</t>
+  </si>
+  <si>
+    <t>ST_044</t>
+  </si>
+  <si>
+    <t>ST_045</t>
+  </si>
+  <si>
+    <t>ST_046</t>
   </si>
 </sst>
 </file>
@@ -11077,7 +11242,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18">
       <c r="A1" s="77" t="s">
-        <v>2036</v>
+        <v>2017</v>
       </c>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -11089,42 +11254,42 @@
     </row>
     <row r="3" spans="1:3" ht="15">
       <c r="A3" s="76" t="s">
-        <v>2035</v>
+        <v>2016</v>
       </c>
       <c r="B3" s="76"/>
       <c r="C3" s="76"/>
     </row>
     <row r="4" spans="1:3" ht="15">
       <c r="A4" s="76" t="s">
-        <v>2034</v>
+        <v>2015</v>
       </c>
       <c r="B4" s="76"/>
       <c r="C4" s="76"/>
     </row>
     <row r="5" spans="1:3" ht="15">
       <c r="A5" s="76" t="s">
-        <v>2033</v>
+        <v>2014</v>
       </c>
       <c r="B5" s="76"/>
       <c r="C5" s="76"/>
     </row>
     <row r="6" spans="1:3" ht="15">
       <c r="A6" s="76" t="s">
-        <v>2032</v>
+        <v>2013</v>
       </c>
       <c r="B6" s="76"/>
       <c r="C6" s="76"/>
     </row>
     <row r="7" spans="1:3" ht="15">
       <c r="A7" s="76" t="s">
-        <v>2031</v>
+        <v>2012</v>
       </c>
       <c r="B7" s="76"/>
       <c r="C7" s="76"/>
     </row>
     <row r="8" spans="1:3" ht="30">
       <c r="A8" s="76" t="s">
-        <v>2030</v>
+        <v>2011</v>
       </c>
       <c r="B8" s="76"/>
       <c r="C8" s="76"/>
@@ -11141,7 +11306,7 @@
     </row>
     <row r="11" spans="1:3" ht="18">
       <c r="A11" s="97" t="s">
-        <v>1959</v>
+        <v>1940</v>
       </c>
       <c r="B11" s="45"/>
       <c r="C11" s="45"/>
@@ -11153,64 +11318,64 @@
     </row>
     <row r="13" spans="1:3" ht="18">
       <c r="A13" s="52" t="s">
-        <v>1960</v>
+        <v>1941</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>1961</v>
+        <v>1942</v>
       </c>
       <c r="C13" s="45"/>
     </row>
     <row r="14" spans="1:3" ht="28">
       <c r="A14" s="45" t="s">
-        <v>2671</v>
+        <v>2599</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>1962</v>
+        <v>1943</v>
       </c>
       <c r="C14" s="45"/>
     </row>
     <row r="15" spans="1:3" ht="28">
       <c r="A15" s="45" t="s">
-        <v>1963</v>
+        <v>1944</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>2672</v>
+        <v>2600</v>
       </c>
       <c r="C15" s="45"/>
     </row>
     <row r="16" spans="1:3" ht="28">
       <c r="A16" s="45" t="s">
-        <v>1964</v>
+        <v>1945</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>2673</v>
+        <v>2601</v>
       </c>
       <c r="C16" s="45"/>
     </row>
     <row r="17" spans="1:3" ht="28">
       <c r="A17" s="45" t="s">
-        <v>1965</v>
+        <v>1946</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>2674</v>
+        <v>2602</v>
       </c>
       <c r="C17" s="45"/>
     </row>
     <row r="18" spans="1:3" ht="28">
       <c r="A18" s="45" t="s">
-        <v>1966</v>
+        <v>1947</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>2675</v>
+        <v>2603</v>
       </c>
       <c r="C18" s="45"/>
     </row>
     <row r="19" spans="1:3" ht="28">
       <c r="A19" s="45" t="s">
-        <v>1967</v>
+        <v>1948</v>
       </c>
       <c r="B19" s="45" t="s">
-        <v>1968</v>
+        <v>1949</v>
       </c>
       <c r="C19" s="45"/>
     </row>
@@ -11226,7 +11391,7 @@
     </row>
     <row r="22" spans="1:3" ht="18">
       <c r="A22" s="97" t="s">
-        <v>1969</v>
+        <v>1950</v>
       </c>
       <c r="B22" s="45"/>
       <c r="C22" s="45"/>
@@ -11238,24 +11403,24 @@
     </row>
     <row r="24" spans="1:3" ht="18">
       <c r="A24" s="52" t="s">
-        <v>1970</v>
+        <v>1951</v>
       </c>
       <c r="B24" s="52" t="s">
         <v>4</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>1971</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="45" t="s">
-        <v>1972</v>
+        <v>1953</v>
       </c>
       <c r="B25" s="45" t="s">
-        <v>1973</v>
+        <v>1954</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>1974</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="28">
@@ -11263,32 +11428,32 @@
         <v>122</v>
       </c>
       <c r="B26" s="45" t="s">
-        <v>2676</v>
+        <v>2604</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>1974</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="28">
       <c r="A27" s="45" t="s">
-        <v>2677</v>
+        <v>2605</v>
       </c>
       <c r="B27" s="45" t="s">
-        <v>2678</v>
+        <v>2606</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>1974</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="28">
       <c r="A28" s="45" t="s">
-        <v>1975</v>
+        <v>1956</v>
       </c>
       <c r="B28" s="45" t="s">
-        <v>1976</v>
+        <v>1957</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>1977</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -11303,7 +11468,7 @@
     </row>
     <row r="31" spans="1:3" ht="18">
       <c r="A31" s="97" t="s">
-        <v>1978</v>
+        <v>1959</v>
       </c>
       <c r="B31" s="45"/>
       <c r="C31" s="45"/>
@@ -11315,7 +11480,7 @@
     </row>
     <row r="33" spans="1:3" ht="18">
       <c r="A33" s="52" t="s">
-        <v>1979</v>
+        <v>1960</v>
       </c>
       <c r="B33" s="52" t="s">
         <v>4</v>
@@ -11324,46 +11489,46 @@
     </row>
     <row r="34" spans="1:3" ht="28">
       <c r="A34" s="45" t="s">
-        <v>1980</v>
+        <v>1961</v>
       </c>
       <c r="B34" s="45" t="s">
-        <v>1981</v>
+        <v>1962</v>
       </c>
       <c r="C34" s="45"/>
     </row>
     <row r="35" spans="1:3" ht="28">
       <c r="A35" s="45" t="s">
-        <v>1982</v>
+        <v>1963</v>
       </c>
       <c r="B35" s="45" t="s">
-        <v>1983</v>
+        <v>1964</v>
       </c>
       <c r="C35" s="45"/>
     </row>
     <row r="36" spans="1:3" ht="28">
       <c r="A36" s="45" t="s">
-        <v>1984</v>
+        <v>1965</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>2679</v>
+        <v>2607</v>
       </c>
       <c r="C36" s="45"/>
     </row>
     <row r="37" spans="1:3" ht="28">
       <c r="A37" s="45" t="s">
-        <v>1985</v>
+        <v>1966</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>2680</v>
+        <v>2608</v>
       </c>
       <c r="C37" s="45"/>
     </row>
     <row r="38" spans="1:3" ht="28">
       <c r="A38" s="45" t="s">
-        <v>2681</v>
+        <v>2609</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>2682</v>
+        <v>2610</v>
       </c>
       <c r="C38" s="45"/>
     </row>
@@ -11379,7 +11544,7 @@
     </row>
     <row r="41" spans="1:3" ht="18">
       <c r="A41" s="97" t="s">
-        <v>1986</v>
+        <v>1967</v>
       </c>
       <c r="B41" s="45"/>
       <c r="C41" s="45"/>
@@ -11391,64 +11556,64 @@
     </row>
     <row r="43" spans="1:3" ht="18">
       <c r="A43" s="52" t="s">
-        <v>1987</v>
+        <v>1968</v>
       </c>
       <c r="B43" s="52" t="s">
-        <v>1961</v>
+        <v>1942</v>
       </c>
       <c r="C43" s="45"/>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="45" t="s">
-        <v>1988</v>
+        <v>1969</v>
       </c>
       <c r="B44" s="45" t="s">
-        <v>1989</v>
+        <v>1970</v>
       </c>
       <c r="C44" s="45"/>
     </row>
     <row r="45" spans="1:3" ht="28">
       <c r="A45" s="45" t="s">
-        <v>1990</v>
+        <v>1971</v>
       </c>
       <c r="B45" s="45" t="s">
-        <v>2683</v>
+        <v>2611</v>
       </c>
       <c r="C45" s="45"/>
     </row>
     <row r="46" spans="1:3" ht="28">
       <c r="A46" s="45" t="s">
-        <v>2684</v>
+        <v>2612</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>2685</v>
+        <v>2613</v>
       </c>
       <c r="C46" s="45"/>
     </row>
     <row r="47" spans="1:3" ht="28">
       <c r="A47" s="45" t="s">
-        <v>2686</v>
+        <v>2614</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>2687</v>
+        <v>2615</v>
       </c>
       <c r="C47" s="45"/>
     </row>
     <row r="48" spans="1:3" ht="28">
       <c r="A48" s="45" t="s">
-        <v>1991</v>
+        <v>1972</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>1992</v>
+        <v>1973</v>
       </c>
       <c r="C48" s="45"/>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="45" t="s">
-        <v>1993</v>
+        <v>1974</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>1994</v>
+        <v>1975</v>
       </c>
       <c r="C49" s="45"/>
     </row>
@@ -11464,7 +11629,7 @@
     </row>
     <row r="52" spans="1:3" ht="18">
       <c r="A52" s="97" t="s">
-        <v>2688</v>
+        <v>2616</v>
       </c>
       <c r="B52" s="45"/>
       <c r="C52" s="45"/>
@@ -11476,13 +11641,13 @@
     </row>
     <row r="54" spans="1:3" ht="18">
       <c r="A54" s="52" t="s">
-        <v>2689</v>
+        <v>2617</v>
       </c>
       <c r="B54" s="52" t="s">
-        <v>2690</v>
+        <v>2618</v>
       </c>
       <c r="C54" s="52" t="s">
-        <v>2691</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="42">
@@ -11490,10 +11655,10 @@
         <v>734</v>
       </c>
       <c r="B55" s="45" t="s">
-        <v>2692</v>
+        <v>2620</v>
       </c>
       <c r="C55" s="45" t="s">
-        <v>2693</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="28">
@@ -11501,10 +11666,10 @@
         <v>725</v>
       </c>
       <c r="B56" s="45" t="s">
-        <v>2694</v>
+        <v>2622</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>2695</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="42">
@@ -11512,10 +11677,10 @@
         <v>819</v>
       </c>
       <c r="B57" s="45" t="s">
-        <v>2696</v>
+        <v>2624</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>2697</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="42">
@@ -11523,10 +11688,10 @@
         <v>753</v>
       </c>
       <c r="B58" s="45" t="s">
-        <v>2698</v>
+        <v>2626</v>
       </c>
       <c r="C58" s="45" t="s">
-        <v>2699</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="70">
@@ -11534,10 +11699,10 @@
         <v>1095</v>
       </c>
       <c r="B59" s="45" t="s">
-        <v>2700</v>
+        <v>2628</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>2701</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -11557,7 +11722,7 @@
     </row>
     <row r="63" spans="1:3" ht="18">
       <c r="A63" s="97" t="s">
-        <v>1995</v>
+        <v>1976</v>
       </c>
       <c r="B63" s="45"/>
       <c r="C63" s="45"/>
@@ -11572,43 +11737,43 @@
         <v>0</v>
       </c>
       <c r="B65" s="52" t="s">
-        <v>1961</v>
+        <v>1942</v>
       </c>
       <c r="C65" s="45"/>
     </row>
     <row r="66" spans="1:3" ht="28">
       <c r="A66" s="45" t="s">
-        <v>1996</v>
+        <v>1977</v>
       </c>
       <c r="B66" s="45" t="s">
-        <v>1997</v>
+        <v>1978</v>
       </c>
       <c r="C66" s="45"/>
     </row>
     <row r="67" spans="1:3" ht="28">
       <c r="A67" s="45" t="s">
-        <v>1998</v>
+        <v>1979</v>
       </c>
       <c r="B67" s="45" t="s">
-        <v>1999</v>
+        <v>1980</v>
       </c>
       <c r="C67" s="45"/>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="45" t="s">
-        <v>2000</v>
+        <v>1981</v>
       </c>
       <c r="B68" s="45" t="s">
-        <v>2001</v>
+        <v>1982</v>
       </c>
       <c r="C68" s="45"/>
     </row>
     <row r="69" spans="1:3" ht="28">
       <c r="A69" s="45" t="s">
-        <v>2002</v>
+        <v>1983</v>
       </c>
       <c r="B69" s="45" t="s">
-        <v>2003</v>
+        <v>1984</v>
       </c>
       <c r="C69" s="45"/>
     </row>
@@ -11624,7 +11789,7 @@
     </row>
     <row r="72" spans="1:3" ht="18">
       <c r="A72" s="97" t="s">
-        <v>2004</v>
+        <v>1985</v>
       </c>
       <c r="B72" s="45"/>
       <c r="C72" s="45"/>
@@ -11636,118 +11801,118 @@
     </row>
     <row r="74" spans="1:3" ht="18">
       <c r="A74" s="52" t="s">
-        <v>2005</v>
+        <v>1986</v>
       </c>
       <c r="B74" s="52" t="s">
-        <v>2006</v>
+        <v>1987</v>
       </c>
       <c r="C74" s="45"/>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="45" t="s">
-        <v>2007</v>
+        <v>1988</v>
       </c>
       <c r="B75" s="45" t="s">
-        <v>2008</v>
+        <v>1989</v>
       </c>
       <c r="C75" s="45"/>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="45" t="s">
-        <v>2009</v>
+        <v>1990</v>
       </c>
       <c r="B76" s="45" t="s">
-        <v>2010</v>
+        <v>1991</v>
       </c>
       <c r="C76" s="45"/>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="45" t="s">
-        <v>2011</v>
+        <v>1992</v>
       </c>
       <c r="B77" s="45" t="s">
-        <v>2012</v>
+        <v>1993</v>
       </c>
       <c r="C77" s="45"/>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="45" t="s">
-        <v>2013</v>
+        <v>1994</v>
       </c>
       <c r="B78" s="45" t="s">
-        <v>2014</v>
+        <v>1995</v>
       </c>
       <c r="C78" s="45"/>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="45" t="s">
-        <v>2015</v>
+        <v>1996</v>
       </c>
       <c r="B79" s="45" t="s">
-        <v>2016</v>
+        <v>1997</v>
       </c>
       <c r="C79" s="45"/>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="45" t="s">
-        <v>2017</v>
+        <v>1998</v>
       </c>
       <c r="B80" s="45" t="s">
-        <v>2018</v>
+        <v>1999</v>
       </c>
       <c r="C80" s="45"/>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="45" t="s">
-        <v>2019</v>
+        <v>2000</v>
       </c>
       <c r="B81" s="45" t="s">
-        <v>2020</v>
+        <v>2001</v>
       </c>
       <c r="C81" s="45"/>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="45" t="s">
-        <v>2021</v>
+        <v>2002</v>
       </c>
       <c r="B82" s="45" t="s">
-        <v>2022</v>
+        <v>2003</v>
       </c>
       <c r="C82" s="45"/>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="45" t="s">
-        <v>2023</v>
+        <v>2004</v>
       </c>
       <c r="B83" s="45" t="s">
-        <v>2702</v>
+        <v>2630</v>
       </c>
       <c r="C83" s="45"/>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="45" t="s">
-        <v>2024</v>
+        <v>2005</v>
       </c>
       <c r="B84" s="45" t="s">
-        <v>2025</v>
+        <v>2006</v>
       </c>
       <c r="C84" s="45"/>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="45" t="s">
-        <v>2026</v>
+        <v>2007</v>
       </c>
       <c r="B85" s="45" t="s">
-        <v>2027</v>
+        <v>2008</v>
       </c>
       <c r="C85" s="45"/>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="45" t="s">
-        <v>2028</v>
+        <v>2009</v>
       </c>
       <c r="B86" s="45" t="s">
-        <v>2029</v>
+        <v>2010</v>
       </c>
       <c r="C86" s="45"/>
     </row>
@@ -13795,7 +13960,7 @@
         <v>61</v>
       </c>
       <c r="G97" s="89" t="s">
-        <v>2553</v>
+        <v>2481</v>
       </c>
       <c r="H97" s="70" t="s">
         <v>62</v>
@@ -13815,7 +13980,7 @@
         <v>745</v>
       </c>
       <c r="G98" s="90" t="s">
-        <v>2554</v>
+        <v>2482</v>
       </c>
       <c r="H98" s="20" t="s">
         <v>62</v>
@@ -14665,10 +14830,10 @@
         <v>745</v>
       </c>
       <c r="G139" s="21" t="s">
-        <v>2555</v>
+        <v>2483</v>
       </c>
       <c r="H139" s="20" t="s">
-        <v>2556</v>
+        <v>2484</v>
       </c>
       <c r="I139" s="21"/>
     </row>
@@ -14879,7 +15044,7 @@
       <c r="C149" s="20"/>
       <c r="D149" s="20"/>
       <c r="E149" s="20" t="s">
-        <v>2557</v>
+        <v>2485</v>
       </c>
       <c r="F149" s="20" t="s">
         <v>773</v>
@@ -14909,7 +15074,7 @@
         <v>768</v>
       </c>
       <c r="G150" s="89" t="s">
-        <v>2559</v>
+        <v>2487</v>
       </c>
       <c r="H150" s="70" t="s">
         <v>1192</v>
@@ -14929,7 +15094,7 @@
         <v>773</v>
       </c>
       <c r="G151" s="90" t="s">
-        <v>2558</v>
+        <v>2486</v>
       </c>
       <c r="H151" s="20" t="s">
         <v>1192</v>
@@ -15203,7 +15368,7 @@
         <v>734</v>
       </c>
       <c r="E164" s="70" t="s">
-        <v>2560</v>
+        <v>2488</v>
       </c>
       <c r="F164" s="70" t="s">
         <v>61</v>
@@ -15223,7 +15388,7 @@
       <c r="C165" s="26"/>
       <c r="D165" s="26"/>
       <c r="E165" s="26" t="s">
-        <v>2560</v>
+        <v>2488</v>
       </c>
       <c r="F165" s="26" t="s">
         <v>745</v>
@@ -15537,7 +15702,7 @@
         <v>725</v>
       </c>
       <c r="G179" s="90" t="s">
-        <v>2561</v>
+        <v>2489</v>
       </c>
       <c r="H179" s="20" t="s">
         <v>63</v>
@@ -16581,7 +16746,7 @@
       <c r="C227" s="26"/>
       <c r="D227" s="26"/>
       <c r="E227" s="26" t="s">
-        <v>2562</v>
+        <v>2490</v>
       </c>
       <c r="F227" s="26" t="s">
         <v>773</v>
@@ -19854,7 +20019,7 @@
         <v>736</v>
       </c>
       <c r="I21" s="45" t="s">
-        <v>2490</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="28">
@@ -19866,7 +20031,7 @@
         <v>1624</v>
       </c>
       <c r="D22" s="45" t="s">
-        <v>2491</v>
+        <v>2419</v>
       </c>
       <c r="E22" s="45" t="s">
         <v>74</v>
@@ -19881,7 +20046,7 @@
         <v>736</v>
       </c>
       <c r="I22" s="45" t="s">
-        <v>2492</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="28">
@@ -20778,7 +20943,7 @@
     <row r="56" spans="1:9" ht="14">
       <c r="A56" s="32"/>
       <c r="B56" s="45" t="s">
-        <v>2493</v>
+        <v>2421</v>
       </c>
       <c r="C56" s="45" t="s">
         <v>42</v>
@@ -20805,7 +20970,7 @@
     <row r="57" spans="1:9" ht="14">
       <c r="A57" s="32"/>
       <c r="B57" s="45" t="s">
-        <v>2494</v>
+        <v>2422</v>
       </c>
       <c r="C57" s="45" t="s">
         <v>42</v>
@@ -20832,7 +20997,7 @@
     <row r="58" spans="1:9" ht="14">
       <c r="A58" s="32"/>
       <c r="B58" s="45" t="s">
-        <v>2495</v>
+        <v>2423</v>
       </c>
       <c r="C58" s="45" t="s">
         <v>42</v>
@@ -20859,7 +21024,7 @@
     <row r="59" spans="1:9" ht="14">
       <c r="A59" s="32"/>
       <c r="B59" s="45" t="s">
-        <v>2496</v>
+        <v>2424</v>
       </c>
       <c r="C59" s="45" t="s">
         <v>42</v>
@@ -20886,7 +21051,7 @@
     <row r="60" spans="1:9" ht="14">
       <c r="A60" s="32"/>
       <c r="B60" s="45" t="s">
-        <v>2497</v>
+        <v>2425</v>
       </c>
       <c r="C60" s="45" t="s">
         <v>42</v>
@@ -20913,7 +21078,7 @@
     <row r="61" spans="1:9" ht="14">
       <c r="A61" s="32"/>
       <c r="B61" s="45" t="s">
-        <v>2498</v>
+        <v>2426</v>
       </c>
       <c r="C61" s="45" t="s">
         <v>42</v>
@@ -20940,7 +21105,7 @@
     <row r="62" spans="1:9" ht="14">
       <c r="A62" s="32"/>
       <c r="B62" s="45" t="s">
-        <v>2499</v>
+        <v>2427</v>
       </c>
       <c r="C62" s="45" t="s">
         <v>42</v>
@@ -20967,7 +21132,7 @@
     <row r="63" spans="1:9" ht="14">
       <c r="A63" s="32"/>
       <c r="B63" s="45" t="s">
-        <v>2500</v>
+        <v>2428</v>
       </c>
       <c r="C63" s="45" t="s">
         <v>42</v>
@@ -20994,7 +21159,7 @@
     <row r="64" spans="1:9" ht="14">
       <c r="A64" s="32"/>
       <c r="B64" s="45" t="s">
-        <v>2501</v>
+        <v>2429</v>
       </c>
       <c r="C64" s="45" t="s">
         <v>42</v>
@@ -21048,7 +21213,7 @@
     <row r="66" spans="1:9" ht="14">
       <c r="A66" s="32"/>
       <c r="B66" s="45" t="s">
-        <v>2502</v>
+        <v>2430</v>
       </c>
       <c r="C66" s="45" t="s">
         <v>42</v>
@@ -21075,7 +21240,7 @@
     <row r="67" spans="1:9" ht="14">
       <c r="A67" s="32"/>
       <c r="B67" s="45" t="s">
-        <v>2503</v>
+        <v>2431</v>
       </c>
       <c r="C67" s="45" t="s">
         <v>42</v>
@@ -21102,7 +21267,7 @@
     <row r="68" spans="1:9" ht="14">
       <c r="A68" s="32"/>
       <c r="B68" s="45" t="s">
-        <v>2504</v>
+        <v>2432</v>
       </c>
       <c r="C68" s="45" t="s">
         <v>42</v>
@@ -21129,7 +21294,7 @@
     <row r="69" spans="1:9" ht="14">
       <c r="A69" s="32"/>
       <c r="B69" s="45" t="s">
-        <v>2505</v>
+        <v>2433</v>
       </c>
       <c r="C69" s="45" t="s">
         <v>42</v>
@@ -21156,7 +21321,7 @@
     <row r="70" spans="1:9" ht="28">
       <c r="A70" s="32"/>
       <c r="B70" s="45" t="s">
-        <v>2506</v>
+        <v>2434</v>
       </c>
       <c r="C70" s="45" t="s">
         <v>42</v>
@@ -21183,7 +21348,7 @@
     <row r="71" spans="1:9" ht="28">
       <c r="A71" s="32"/>
       <c r="B71" s="45" t="s">
-        <v>2507</v>
+        <v>2435</v>
       </c>
       <c r="C71" s="45" t="s">
         <v>42</v>
@@ -21210,7 +21375,7 @@
     <row r="72" spans="1:9" ht="28">
       <c r="A72" s="32"/>
       <c r="B72" s="45" t="s">
-        <v>2508</v>
+        <v>2436</v>
       </c>
       <c r="C72" s="45" t="s">
         <v>42</v>
@@ -21237,7 +21402,7 @@
     <row r="73" spans="1:9" ht="28">
       <c r="A73" s="32"/>
       <c r="B73" s="45" t="s">
-        <v>2509</v>
+        <v>2437</v>
       </c>
       <c r="C73" s="45" t="s">
         <v>42</v>
@@ -21264,7 +21429,7 @@
     <row r="74" spans="1:9" ht="28">
       <c r="A74" s="32"/>
       <c r="B74" s="45" t="s">
-        <v>2510</v>
+        <v>2438</v>
       </c>
       <c r="C74" s="45" t="s">
         <v>42</v>
@@ -21291,7 +21456,7 @@
     <row r="75" spans="1:9" ht="28">
       <c r="A75" s="32"/>
       <c r="B75" s="45" t="s">
-        <v>2511</v>
+        <v>2439</v>
       </c>
       <c r="C75" s="45" t="s">
         <v>42</v>
@@ -21318,7 +21483,7 @@
     <row r="76" spans="1:9" ht="14">
       <c r="A76" s="32"/>
       <c r="B76" s="45" t="s">
-        <v>2512</v>
+        <v>2440</v>
       </c>
       <c r="C76" s="45" t="s">
         <v>43</v>
@@ -21345,7 +21510,7 @@
     <row r="77" spans="1:9" ht="14">
       <c r="A77" s="32"/>
       <c r="B77" s="45" t="s">
-        <v>2513</v>
+        <v>2441</v>
       </c>
       <c r="C77" s="45" t="s">
         <v>43</v>
@@ -21372,7 +21537,7 @@
     <row r="78" spans="1:9" ht="28">
       <c r="A78" s="32"/>
       <c r="B78" s="45" t="s">
-        <v>2514</v>
+        <v>2442</v>
       </c>
       <c r="C78" s="45" t="s">
         <v>43</v>
@@ -21399,7 +21564,7 @@
     <row r="79" spans="1:9" ht="14">
       <c r="A79" s="32"/>
       <c r="B79" s="45" t="s">
-        <v>2515</v>
+        <v>2443</v>
       </c>
       <c r="C79" s="45" t="s">
         <v>43</v>
@@ -21426,7 +21591,7 @@
     <row r="80" spans="1:9" ht="28">
       <c r="A80" s="32"/>
       <c r="B80" s="45" t="s">
-        <v>2516</v>
+        <v>2444</v>
       </c>
       <c r="C80" s="45" t="s">
         <v>43</v>
@@ -21453,7 +21618,7 @@
     <row r="81" spans="1:9" ht="14">
       <c r="A81" s="32"/>
       <c r="B81" s="45" t="s">
-        <v>2517</v>
+        <v>2445</v>
       </c>
       <c r="C81" s="45" t="s">
         <v>43</v>
@@ -21480,7 +21645,7 @@
     <row r="82" spans="1:9" ht="14">
       <c r="A82" s="32"/>
       <c r="B82" s="45" t="s">
-        <v>2518</v>
+        <v>2446</v>
       </c>
       <c r="C82" s="45" t="s">
         <v>43</v>
@@ -21507,7 +21672,7 @@
     <row r="83" spans="1:9" ht="28">
       <c r="A83" s="32"/>
       <c r="B83" s="45" t="s">
-        <v>2519</v>
+        <v>2447</v>
       </c>
       <c r="C83" s="45" t="s">
         <v>43</v>
@@ -21534,7 +21699,7 @@
     <row r="84" spans="1:9" ht="28">
       <c r="A84" s="32"/>
       <c r="B84" s="45" t="s">
-        <v>2520</v>
+        <v>2448</v>
       </c>
       <c r="C84" s="45" t="s">
         <v>43</v>
@@ -21561,7 +21726,7 @@
     <row r="85" spans="1:9" ht="14">
       <c r="A85" s="32"/>
       <c r="B85" s="45" t="s">
-        <v>2521</v>
+        <v>2449</v>
       </c>
       <c r="C85" s="45" t="s">
         <v>43</v>
@@ -21588,7 +21753,7 @@
     <row r="86" spans="1:9" ht="28">
       <c r="A86" s="32"/>
       <c r="B86" s="45" t="s">
-        <v>2522</v>
+        <v>2450</v>
       </c>
       <c r="C86" s="45" t="s">
         <v>43</v>
@@ -21615,7 +21780,7 @@
     <row r="87" spans="1:9" ht="28">
       <c r="A87" s="32"/>
       <c r="B87" s="45" t="s">
-        <v>2523</v>
+        <v>2451</v>
       </c>
       <c r="C87" s="45" t="s">
         <v>43</v>
@@ -21642,7 +21807,7 @@
     <row r="88" spans="1:9" ht="28">
       <c r="A88" s="32"/>
       <c r="B88" s="45" t="s">
-        <v>2524</v>
+        <v>2452</v>
       </c>
       <c r="C88" s="45" t="s">
         <v>43</v>
@@ -21669,7 +21834,7 @@
     <row r="89" spans="1:9" ht="28">
       <c r="A89" s="32"/>
       <c r="B89" s="45" t="s">
-        <v>2525</v>
+        <v>2453</v>
       </c>
       <c r="C89" s="45" t="s">
         <v>43</v>
@@ -21696,7 +21861,7 @@
     <row r="90" spans="1:9" ht="14">
       <c r="A90" s="32"/>
       <c r="B90" s="45" t="s">
-        <v>2526</v>
+        <v>2454</v>
       </c>
       <c r="C90" s="45" t="s">
         <v>43</v>
@@ -21723,7 +21888,7 @@
     <row r="91" spans="1:9" ht="14">
       <c r="A91" s="32"/>
       <c r="B91" s="45" t="s">
-        <v>2527</v>
+        <v>2455</v>
       </c>
       <c r="C91" s="45" t="s">
         <v>43</v>
@@ -21750,7 +21915,7 @@
     <row r="92" spans="1:9" ht="28">
       <c r="A92" s="32"/>
       <c r="B92" s="45" t="s">
-        <v>2528</v>
+        <v>2456</v>
       </c>
       <c r="C92" s="45" t="s">
         <v>43</v>
@@ -21777,7 +21942,7 @@
     <row r="93" spans="1:9" ht="14">
       <c r="A93" s="32"/>
       <c r="B93" s="45" t="s">
-        <v>2529</v>
+        <v>2457</v>
       </c>
       <c r="C93" s="45" t="s">
         <v>43</v>
@@ -21804,7 +21969,7 @@
     <row r="94" spans="1:9" ht="28">
       <c r="A94" s="32"/>
       <c r="B94" s="45" t="s">
-        <v>2530</v>
+        <v>2458</v>
       </c>
       <c r="C94" s="45" t="s">
         <v>43</v>
@@ -21831,7 +21996,7 @@
     <row r="95" spans="1:9" ht="14">
       <c r="A95" s="32"/>
       <c r="B95" s="45" t="s">
-        <v>2531</v>
+        <v>2459</v>
       </c>
       <c r="C95" s="45" t="s">
         <v>43</v>
@@ -21858,7 +22023,7 @@
     <row r="96" spans="1:9" ht="14">
       <c r="A96" s="32"/>
       <c r="B96" s="45" t="s">
-        <v>2532</v>
+        <v>2460</v>
       </c>
       <c r="C96" s="45" t="s">
         <v>43</v>
@@ -21885,7 +22050,7 @@
     <row r="97" spans="1:9" ht="14">
       <c r="A97" s="32"/>
       <c r="B97" s="45" t="s">
-        <v>2533</v>
+        <v>2461</v>
       </c>
       <c r="C97" s="45" t="s">
         <v>43</v>
@@ -21912,7 +22077,7 @@
     <row r="98" spans="1:9" ht="14">
       <c r="A98" s="32"/>
       <c r="B98" s="45" t="s">
-        <v>2534</v>
+        <v>2462</v>
       </c>
       <c r="C98" s="45" t="s">
         <v>43</v>
@@ -21939,7 +22104,7 @@
     <row r="99" spans="1:9" ht="14">
       <c r="A99" s="32"/>
       <c r="B99" s="45" t="s">
-        <v>2535</v>
+        <v>2463</v>
       </c>
       <c r="C99" s="45" t="s">
         <v>43</v>
@@ -21966,7 +22131,7 @@
     <row r="100" spans="1:9" ht="14">
       <c r="A100" s="32"/>
       <c r="B100" s="45" t="s">
-        <v>2536</v>
+        <v>2464</v>
       </c>
       <c r="C100" s="45" t="s">
         <v>45</v>
@@ -21993,7 +22158,7 @@
     <row r="101" spans="1:9" ht="14">
       <c r="A101" s="32"/>
       <c r="B101" s="45" t="s">
-        <v>2537</v>
+        <v>2465</v>
       </c>
       <c r="C101" s="45" t="s">
         <v>45</v>
@@ -22695,7 +22860,7 @@
     <row r="127" spans="1:9" ht="28">
       <c r="A127" s="32"/>
       <c r="B127" s="45" t="s">
-        <v>2538</v>
+        <v>2466</v>
       </c>
       <c r="C127" s="45" t="s">
         <v>1632</v>
@@ -22722,7 +22887,7 @@
     <row r="128" spans="1:9" ht="14">
       <c r="A128" s="32"/>
       <c r="B128" s="45" t="s">
-        <v>2539</v>
+        <v>2467</v>
       </c>
       <c r="C128" s="45" t="s">
         <v>41</v>
@@ -22851,7 +23016,7 @@
         <v>736</v>
       </c>
       <c r="I132" s="45" t="s">
-        <v>2540</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="28">
@@ -22878,7 +23043,7 @@
         <v>736</v>
       </c>
       <c r="I133" s="45" t="s">
-        <v>2541</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="14">
@@ -23580,7 +23745,7 @@
         <v>736</v>
       </c>
       <c r="I159" s="45" t="s">
-        <v>2542</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="14">
@@ -23835,7 +24000,7 @@
         <v>42</v>
       </c>
       <c r="D169" s="45" t="s">
-        <v>2543</v>
+        <v>2471</v>
       </c>
       <c r="E169" s="45" t="s">
         <v>1660</v>
@@ -23904,7 +24069,7 @@
         <v>736</v>
       </c>
       <c r="I171" s="45" t="s">
-        <v>2544</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="28">
@@ -24240,7 +24405,7 @@
         <v>42</v>
       </c>
       <c r="D184" s="45" t="s">
-        <v>2545</v>
+        <v>2473</v>
       </c>
       <c r="E184" s="45" t="s">
         <v>74</v>
@@ -24267,7 +24432,7 @@
         <v>42</v>
       </c>
       <c r="D185" s="45" t="s">
-        <v>2546</v>
+        <v>2474</v>
       </c>
       <c r="E185" s="45" t="s">
         <v>74</v>
@@ -24660,7 +24825,7 @@
         <v>736</v>
       </c>
       <c r="I199" s="45" t="s">
-        <v>2547</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="200" spans="1:9" ht="28">
@@ -25125,7 +25290,7 @@
     <row r="217" spans="1:9" ht="28">
       <c r="A217" s="32"/>
       <c r="B217" s="45" t="s">
-        <v>2548</v>
+        <v>2476</v>
       </c>
       <c r="C217" s="45" t="s">
         <v>44</v>
@@ -25152,7 +25317,7 @@
     <row r="218" spans="1:9" ht="28">
       <c r="A218" s="32"/>
       <c r="B218" s="45" t="s">
-        <v>2549</v>
+        <v>2477</v>
       </c>
       <c r="C218" s="45" t="s">
         <v>44</v>
@@ -25611,7 +25776,7 @@
     <row r="235" spans="1:9" ht="28">
       <c r="A235" s="32"/>
       <c r="B235" s="45" t="s">
-        <v>2550</v>
+        <v>2478</v>
       </c>
       <c r="C235" s="45" t="s">
         <v>44</v>
@@ -25719,7 +25884,7 @@
     <row r="239" spans="1:9" ht="28">
       <c r="A239" s="32"/>
       <c r="B239" s="45" t="s">
-        <v>2551</v>
+        <v>2479</v>
       </c>
       <c r="C239" s="45" t="s">
         <v>44</v>
@@ -25941,7 +26106,7 @@
         <v>41</v>
       </c>
       <c r="D247" s="45" t="s">
-        <v>2552</v>
+        <v>2480</v>
       </c>
       <c r="E247" s="45" t="s">
         <v>74</v>
@@ -28170,7 +28335,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A2:G79"/>
+  <dimension ref="A2:G165"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -28213,40 +28378,46 @@
         <v>80</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>2390</v>
+        <v>2321</v>
       </c>
       <c r="D3" s="34" t="s">
         <v>1881</v>
       </c>
-      <c r="E3" s="34"/>
+      <c r="E3" s="34" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="45"/>
       <c r="B4" s="34"/>
       <c r="C4" s="34" t="s">
-        <v>2391</v>
+        <v>2322</v>
       </c>
       <c r="D4" s="34" t="s">
         <v>1882</v>
       </c>
-      <c r="E4" s="34"/>
+      <c r="E4" s="34" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="45"/>
       <c r="B5" s="34"/>
       <c r="C5" s="34" t="s">
-        <v>2392</v>
+        <v>2323</v>
       </c>
       <c r="D5" s="34" t="s">
         <v>1883</v>
       </c>
-      <c r="E5" s="34"/>
+      <c r="E5" s="34" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="45"/>
       <c r="B6" s="34"/>
       <c r="C6" s="34" t="s">
-        <v>2393</v>
+        <v>2324</v>
       </c>
       <c r="D6" s="34" t="s">
         <v>1884</v>
@@ -28259,7 +28430,7 @@
       <c r="A7" s="45"/>
       <c r="B7" s="34"/>
       <c r="C7" s="34" t="s">
-        <v>2394</v>
+        <v>2325</v>
       </c>
       <c r="D7" s="34" t="s">
         <v>1886</v>
@@ -28272,126 +28443,140 @@
       <c r="A8" s="45"/>
       <c r="B8" s="34"/>
       <c r="C8" s="34" t="s">
-        <v>2395</v>
+        <v>2645</v>
       </c>
       <c r="D8" s="34" t="s">
         <v>1887</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="45"/>
       <c r="B9" s="34"/>
       <c r="C9" s="34" t="s">
-        <v>2396</v>
+        <v>2646</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="45"/>
       <c r="B10" s="34"/>
       <c r="C10" s="34" t="s">
-        <v>2397</v>
+        <v>2647</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="45"/>
       <c r="B11" s="34"/>
       <c r="C11" s="34" t="s">
-        <v>2398</v>
+        <v>2326</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>1891</v>
-      </c>
-      <c r="E11" s="34"/>
+        <v>1890</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="45"/>
       <c r="B12" s="34"/>
       <c r="C12" s="34" t="s">
-        <v>2399</v>
+        <v>2327</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>1892</v>
-      </c>
-      <c r="E12" s="34"/>
+        <v>1891</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="45"/>
       <c r="B13" s="34"/>
       <c r="C13" s="34" t="s">
-        <v>2400</v>
+        <v>2328</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>1893</v>
-      </c>
-      <c r="E13" s="34"/>
+        <v>1892</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="45"/>
       <c r="B14" s="34"/>
       <c r="C14" s="34" t="s">
-        <v>2401</v>
+        <v>2329</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>1894</v>
-      </c>
-      <c r="E14" s="34"/>
+        <v>1893</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="45"/>
       <c r="B15" s="34"/>
       <c r="C15" s="34" t="s">
-        <v>2402</v>
+        <v>2330</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>1895</v>
-      </c>
-      <c r="E15" s="34"/>
+        <v>1894</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="45"/>
       <c r="B16" s="34"/>
       <c r="C16" s="34" t="s">
-        <v>2403</v>
+        <v>2331</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>1896</v>
-      </c>
-      <c r="E16" s="34"/>
+        <v>1895</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1">
       <c r="A17" s="45"/>
       <c r="B17" s="34"/>
       <c r="C17" s="34" t="s">
-        <v>2404</v>
+        <v>2332</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>1897</v>
-      </c>
-      <c r="E17" s="34"/>
+        <v>1896</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1">
       <c r="A18" s="45"/>
       <c r="B18" s="34"/>
       <c r="C18" s="34" t="s">
-        <v>2405</v>
+        <v>2333</v>
       </c>
       <c r="D18" s="34" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="E18" s="34" t="s">
         <v>1885</v>
@@ -28401,10 +28586,10 @@
       <c r="A19" s="45"/>
       <c r="B19" s="34"/>
       <c r="C19" s="34" t="s">
-        <v>2406</v>
+        <v>2334</v>
       </c>
       <c r="D19" s="34" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="E19" s="34" t="s">
         <v>1885</v>
@@ -28414,10 +28599,10 @@
       <c r="A20" s="45"/>
       <c r="B20" s="34"/>
       <c r="C20" s="34" t="s">
-        <v>2407</v>
+        <v>2335</v>
       </c>
       <c r="D20" s="34" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="E20" s="34" t="s">
         <v>1885</v>
@@ -28427,10 +28612,10 @@
       <c r="A21" s="45"/>
       <c r="B21" s="34"/>
       <c r="C21" s="34" t="s">
-        <v>2408</v>
+        <v>2336</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="E21" s="34" t="s">
         <v>1885</v>
@@ -28440,10 +28625,10 @@
       <c r="A22" s="45"/>
       <c r="B22" s="34"/>
       <c r="C22" s="34" t="s">
-        <v>2409</v>
+        <v>2337</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="E22" s="34" t="s">
         <v>1885</v>
@@ -28453,10 +28638,10 @@
       <c r="A23" s="45"/>
       <c r="B23" s="34"/>
       <c r="C23" s="34" t="s">
-        <v>2410</v>
+        <v>2338</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="E23" s="34" t="s">
         <v>1885</v>
@@ -28466,10 +28651,10 @@
       <c r="A24" s="45"/>
       <c r="B24" s="34"/>
       <c r="C24" s="34" t="s">
-        <v>2411</v>
+        <v>2339</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="E24" s="34" t="s">
         <v>1885</v>
@@ -28479,10 +28664,10 @@
       <c r="A25" s="45"/>
       <c r="B25" s="34"/>
       <c r="C25" s="34" t="s">
-        <v>2412</v>
+        <v>2340</v>
       </c>
       <c r="D25" s="34" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="E25" s="34" t="s">
         <v>1885</v>
@@ -28492,10 +28677,10 @@
       <c r="A26" s="45"/>
       <c r="B26" s="34"/>
       <c r="C26" s="34" t="s">
-        <v>2413</v>
+        <v>2341</v>
       </c>
       <c r="D26" s="34" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="E26" s="34" t="s">
         <v>1885</v>
@@ -28505,10 +28690,10 @@
       <c r="A27" s="45"/>
       <c r="B27" s="34"/>
       <c r="C27" s="34" t="s">
-        <v>2414</v>
+        <v>2342</v>
       </c>
       <c r="D27" s="34" t="s">
-        <v>2415</v>
+        <v>2343</v>
       </c>
       <c r="E27" s="34" t="s">
         <v>1885</v>
@@ -28518,10 +28703,10 @@
       <c r="A28" s="45"/>
       <c r="B28" s="34"/>
       <c r="C28" s="34" t="s">
-        <v>2416</v>
+        <v>2344</v>
       </c>
       <c r="D28" s="34" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="E28" s="34" t="s">
         <v>1885</v>
@@ -28531,10 +28716,10 @@
       <c r="A29" s="45"/>
       <c r="B29" s="34"/>
       <c r="C29" s="34" t="s">
-        <v>2417</v>
+        <v>2345</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="E29" s="34" t="s">
         <v>1885</v>
@@ -28548,463 +28733,547 @@
         <v>36</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>2418</v>
+        <v>2346</v>
       </c>
       <c r="D30" s="35" t="s">
-        <v>1909</v>
-      </c>
-      <c r="E30" s="35"/>
+        <v>1908</v>
+      </c>
+      <c r="E30" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="31" spans="1:5" ht="15.75" customHeight="1">
       <c r="A31" s="45"/>
       <c r="B31" s="35"/>
       <c r="C31" s="35" t="s">
-        <v>2419</v>
+        <v>2347</v>
       </c>
       <c r="D31" s="35" t="s">
-        <v>1910</v>
-      </c>
-      <c r="E31" s="35"/>
+        <v>1909</v>
+      </c>
+      <c r="E31" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1">
       <c r="A32" s="45"/>
       <c r="B32" s="35"/>
       <c r="C32" s="35" t="s">
-        <v>2420</v>
+        <v>2348</v>
       </c>
       <c r="D32" s="35" t="s">
-        <v>1911</v>
-      </c>
-      <c r="E32" s="35"/>
+        <v>1910</v>
+      </c>
+      <c r="E32" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="33" spans="1:5" ht="15.75" customHeight="1">
       <c r="A33" s="45"/>
       <c r="B33" s="35"/>
       <c r="C33" s="35" t="s">
-        <v>2421</v>
+        <v>2349</v>
       </c>
       <c r="D33" s="35" t="s">
-        <v>1912</v>
-      </c>
-      <c r="E33" s="35"/>
+        <v>1911</v>
+      </c>
+      <c r="E33" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="34" spans="1:5" ht="15.75" customHeight="1">
       <c r="A34" s="45"/>
       <c r="B34" s="35"/>
       <c r="C34" s="35" t="s">
-        <v>2422</v>
+        <v>2350</v>
       </c>
       <c r="D34" s="35" t="s">
-        <v>1913</v>
-      </c>
-      <c r="E34" s="35"/>
+        <v>1912</v>
+      </c>
+      <c r="E34" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="35" spans="1:5" ht="15.75" customHeight="1">
       <c r="A35" s="45"/>
       <c r="B35" s="35"/>
       <c r="C35" s="35" t="s">
-        <v>2423</v>
+        <v>2351</v>
       </c>
       <c r="D35" s="35" t="s">
-        <v>1914</v>
-      </c>
-      <c r="E35" s="35"/>
+        <v>1913</v>
+      </c>
+      <c r="E35" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="36" spans="1:5" ht="15.75" customHeight="1">
       <c r="A36" s="45"/>
       <c r="B36" s="35"/>
       <c r="C36" s="35" t="s">
-        <v>2424</v>
+        <v>2352</v>
       </c>
       <c r="D36" s="35" t="s">
-        <v>1915</v>
-      </c>
-      <c r="E36" s="35"/>
+        <v>1914</v>
+      </c>
+      <c r="E36" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="37" spans="1:5" ht="15.75" customHeight="1">
       <c r="A37" s="45"/>
       <c r="B37" s="35"/>
       <c r="C37" s="35" t="s">
-        <v>2425</v>
+        <v>2353</v>
       </c>
       <c r="D37" s="35" t="s">
-        <v>1916</v>
-      </c>
-      <c r="E37" s="35"/>
+        <v>1915</v>
+      </c>
+      <c r="E37" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="38" spans="1:5" ht="15.75" customHeight="1">
       <c r="A38" s="45"/>
       <c r="B38" s="35"/>
       <c r="C38" s="35" t="s">
-        <v>2426</v>
+        <v>2354</v>
       </c>
       <c r="D38" s="35" t="s">
-        <v>2427</v>
-      </c>
-      <c r="E38" s="35"/>
+        <v>2355</v>
+      </c>
+      <c r="E38" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="39" spans="1:5" ht="15.75" customHeight="1">
       <c r="A39" s="45"/>
       <c r="B39" s="35"/>
       <c r="C39" s="35" t="s">
-        <v>2428</v>
+        <v>2356</v>
       </c>
       <c r="D39" s="35" t="s">
-        <v>2429</v>
-      </c>
-      <c r="E39" s="35"/>
+        <v>2357</v>
+      </c>
+      <c r="E39" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="40" spans="1:5" ht="15.75" customHeight="1">
       <c r="A40" s="45"/>
       <c r="B40" s="35"/>
       <c r="C40" s="35" t="s">
-        <v>2430</v>
+        <v>2358</v>
       </c>
       <c r="D40" s="35" t="s">
-        <v>2431</v>
-      </c>
-      <c r="E40" s="35"/>
+        <v>2359</v>
+      </c>
+      <c r="E40" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="41" spans="1:5" ht="15.75" customHeight="1">
       <c r="A41" s="45"/>
       <c r="B41" s="35"/>
       <c r="C41" s="35" t="s">
-        <v>2432</v>
+        <v>2360</v>
       </c>
       <c r="D41" s="35" t="s">
-        <v>2433</v>
-      </c>
-      <c r="E41" s="35"/>
+        <v>2361</v>
+      </c>
+      <c r="E41" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" customHeight="1">
       <c r="A42" s="45"/>
       <c r="B42" s="35"/>
       <c r="C42" s="35" t="s">
-        <v>2434</v>
+        <v>2362</v>
       </c>
       <c r="D42" s="35" t="s">
-        <v>1917</v>
-      </c>
-      <c r="E42" s="35"/>
+        <v>1916</v>
+      </c>
+      <c r="E42" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" customHeight="1">
       <c r="A43" s="45"/>
       <c r="B43" s="35"/>
       <c r="C43" s="35" t="s">
-        <v>2435</v>
+        <v>2363</v>
       </c>
       <c r="D43" s="35" t="s">
-        <v>1918</v>
-      </c>
-      <c r="E43" s="35"/>
+        <v>1917</v>
+      </c>
+      <c r="E43" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="44" spans="1:5" ht="15.75" customHeight="1">
       <c r="A44" s="45"/>
       <c r="B44" s="35"/>
       <c r="C44" s="35" t="s">
-        <v>2436</v>
+        <v>2364</v>
       </c>
       <c r="D44" s="35" t="s">
-        <v>1919</v>
-      </c>
-      <c r="E44" s="35"/>
+        <v>1918</v>
+      </c>
+      <c r="E44" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="45" spans="1:5" ht="15.75" customHeight="1">
       <c r="A45" s="45"/>
       <c r="B45" s="35"/>
       <c r="C45" s="35" t="s">
-        <v>2437</v>
+        <v>2365</v>
       </c>
       <c r="D45" s="35" t="s">
-        <v>1920</v>
-      </c>
-      <c r="E45" s="35"/>
+        <v>1919</v>
+      </c>
+      <c r="E45" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="46" spans="1:5" ht="15.75" customHeight="1">
       <c r="A46" s="45"/>
       <c r="B46" s="35"/>
       <c r="C46" s="35" t="s">
-        <v>2438</v>
+        <v>2366</v>
       </c>
       <c r="D46" s="35" t="s">
-        <v>1921</v>
-      </c>
-      <c r="E46" s="35"/>
+        <v>1920</v>
+      </c>
+      <c r="E46" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="47" spans="1:5" ht="15.75" customHeight="1">
       <c r="A47" s="45"/>
       <c r="B47" s="35"/>
       <c r="C47" s="35" t="s">
-        <v>2439</v>
+        <v>2367</v>
       </c>
       <c r="D47" s="35" t="s">
-        <v>1922</v>
-      </c>
-      <c r="E47" s="35"/>
+        <v>1921</v>
+      </c>
+      <c r="E47" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="48" spans="1:5" ht="15.75" customHeight="1">
       <c r="A48" s="45"/>
       <c r="B48" s="35"/>
       <c r="C48" s="35" t="s">
-        <v>2440</v>
+        <v>2368</v>
       </c>
       <c r="D48" s="35" t="s">
-        <v>1923</v>
-      </c>
-      <c r="E48" s="35"/>
+        <v>1922</v>
+      </c>
+      <c r="E48" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="49" spans="1:5" ht="15.75" customHeight="1">
       <c r="A49" s="45"/>
       <c r="B49" s="35"/>
       <c r="C49" s="35" t="s">
-        <v>2441</v>
+        <v>2369</v>
       </c>
       <c r="D49" s="35" t="s">
-        <v>1924</v>
-      </c>
-      <c r="E49" s="35"/>
+        <v>1923</v>
+      </c>
+      <c r="E49" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="50" spans="1:5" ht="15.75" customHeight="1">
       <c r="A50" s="45"/>
       <c r="B50" s="35"/>
       <c r="C50" s="35" t="s">
-        <v>2442</v>
+        <v>2370</v>
       </c>
       <c r="D50" s="35" t="s">
-        <v>2443</v>
-      </c>
-      <c r="E50" s="35"/>
+        <v>2371</v>
+      </c>
+      <c r="E50" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="51" spans="1:5" ht="15.75" customHeight="1">
       <c r="A51" s="45"/>
       <c r="B51" s="35"/>
       <c r="C51" s="35" t="s">
-        <v>2444</v>
+        <v>2372</v>
       </c>
       <c r="D51" s="35" t="s">
-        <v>1925</v>
-      </c>
-      <c r="E51" s="35"/>
+        <v>1924</v>
+      </c>
+      <c r="E51" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="52" spans="1:5" ht="15.75" customHeight="1">
       <c r="A52" s="45"/>
       <c r="B52" s="35"/>
       <c r="C52" s="35" t="s">
-        <v>2445</v>
+        <v>2373</v>
       </c>
       <c r="D52" s="35" t="s">
-        <v>1926</v>
-      </c>
-      <c r="E52" s="35"/>
+        <v>1925</v>
+      </c>
+      <c r="E52" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="53" spans="1:5" ht="15.75" customHeight="1">
       <c r="A53" s="45"/>
       <c r="B53" s="35"/>
       <c r="C53" s="35" t="s">
-        <v>2446</v>
+        <v>2374</v>
       </c>
       <c r="D53" s="35" t="s">
-        <v>1927</v>
-      </c>
-      <c r="E53" s="35"/>
+        <v>1926</v>
+      </c>
+      <c r="E53" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="54" spans="1:5" ht="15.75" customHeight="1">
       <c r="A54" s="45"/>
       <c r="B54" s="35"/>
       <c r="C54" s="35" t="s">
-        <v>2447</v>
+        <v>2375</v>
       </c>
       <c r="D54" s="35" t="s">
-        <v>1928</v>
-      </c>
-      <c r="E54" s="35"/>
+        <v>1927</v>
+      </c>
+      <c r="E54" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="55" spans="1:5" ht="15.75" customHeight="1">
       <c r="A55" s="45"/>
       <c r="B55" s="35"/>
       <c r="C55" s="35" t="s">
-        <v>2448</v>
+        <v>2376</v>
       </c>
       <c r="D55" s="35" t="s">
-        <v>1929</v>
-      </c>
-      <c r="E55" s="35"/>
+        <v>1928</v>
+      </c>
+      <c r="E55" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="56" spans="1:5" ht="15.75" customHeight="1">
       <c r="A56" s="45"/>
       <c r="B56" s="35"/>
       <c r="C56" s="35" t="s">
-        <v>2449</v>
+        <v>2377</v>
       </c>
       <c r="D56" s="35" t="s">
-        <v>2450</v>
-      </c>
-      <c r="E56" s="35"/>
+        <v>2378</v>
+      </c>
+      <c r="E56" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="57" spans="1:5" ht="15.75" customHeight="1">
       <c r="A57" s="45"/>
       <c r="B57" s="35"/>
       <c r="C57" s="35" t="s">
-        <v>2451</v>
+        <v>2379</v>
       </c>
       <c r="D57" s="35" t="s">
-        <v>2452</v>
-      </c>
-      <c r="E57" s="35"/>
+        <v>2380</v>
+      </c>
+      <c r="E57" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="58" spans="1:5" ht="15.75" customHeight="1">
       <c r="A58" s="45"/>
       <c r="B58" s="35"/>
       <c r="C58" s="35" t="s">
-        <v>2453</v>
+        <v>2381</v>
       </c>
       <c r="D58" s="35" t="s">
-        <v>2454</v>
-      </c>
-      <c r="E58" s="35"/>
+        <v>2382</v>
+      </c>
+      <c r="E58" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="59" spans="1:5" ht="15.75" customHeight="1">
       <c r="A59" s="45"/>
       <c r="B59" s="35"/>
       <c r="C59" s="35" t="s">
-        <v>2455</v>
+        <v>2383</v>
       </c>
       <c r="D59" s="35" t="s">
-        <v>2456</v>
-      </c>
-      <c r="E59" s="35"/>
+        <v>2384</v>
+      </c>
+      <c r="E59" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="60" spans="1:5" ht="15.75" customHeight="1">
       <c r="A60" s="45"/>
       <c r="B60" s="35"/>
       <c r="C60" s="35" t="s">
-        <v>2457</v>
+        <v>2385</v>
       </c>
       <c r="D60" s="35" t="s">
-        <v>2458</v>
-      </c>
-      <c r="E60" s="35"/>
+        <v>2386</v>
+      </c>
+      <c r="E60" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="61" spans="1:5" ht="15.75" customHeight="1">
       <c r="A61" s="45"/>
       <c r="B61" s="35"/>
       <c r="C61" s="35" t="s">
-        <v>2459</v>
+        <v>2387</v>
       </c>
       <c r="D61" s="35" t="s">
-        <v>2460</v>
-      </c>
-      <c r="E61" s="35"/>
+        <v>2388</v>
+      </c>
+      <c r="E61" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="62" spans="1:5" ht="15.75" customHeight="1">
       <c r="A62" s="45"/>
       <c r="B62" s="35"/>
       <c r="C62" s="35" t="s">
-        <v>2461</v>
+        <v>2389</v>
       </c>
       <c r="D62" s="35" t="s">
-        <v>2462</v>
-      </c>
-      <c r="E62" s="35"/>
+        <v>2390</v>
+      </c>
+      <c r="E62" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="63" spans="1:5" ht="15.75" customHeight="1">
       <c r="A63" s="45"/>
       <c r="B63" s="35"/>
       <c r="C63" s="35" t="s">
-        <v>2463</v>
+        <v>2391</v>
       </c>
       <c r="D63" s="35" t="s">
-        <v>2464</v>
-      </c>
-      <c r="E63" s="35"/>
+        <v>2392</v>
+      </c>
+      <c r="E63" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="64" spans="1:5" ht="15.75" customHeight="1">
       <c r="A64" s="45"/>
       <c r="B64" s="35"/>
       <c r="C64" s="35" t="s">
-        <v>2465</v>
+        <v>2393</v>
       </c>
       <c r="D64" s="35" t="s">
-        <v>1930</v>
-      </c>
-      <c r="E64" s="35"/>
+        <v>1929</v>
+      </c>
+      <c r="E64" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="65" spans="1:5" ht="15.75" customHeight="1">
       <c r="A65" s="45"/>
       <c r="B65" s="35"/>
       <c r="C65" s="35" t="s">
-        <v>2466</v>
+        <v>2394</v>
       </c>
       <c r="D65" s="35" t="s">
-        <v>1931</v>
-      </c>
-      <c r="E65" s="35"/>
+        <v>2648</v>
+      </c>
+      <c r="E65" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="66" spans="1:5" ht="15.75" customHeight="1">
       <c r="A66" s="45"/>
       <c r="B66" s="35"/>
       <c r="C66" s="35" t="s">
-        <v>2467</v>
+        <v>2395</v>
       </c>
       <c r="D66" s="35" t="s">
-        <v>1932</v>
-      </c>
-      <c r="E66" s="35"/>
+        <v>2649</v>
+      </c>
+      <c r="E66" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" customHeight="1">
       <c r="A67" s="45"/>
       <c r="B67" s="35"/>
       <c r="C67" s="35" t="s">
-        <v>2468</v>
+        <v>2396</v>
       </c>
       <c r="D67" s="35" t="s">
-        <v>2469</v>
-      </c>
-      <c r="E67" s="35"/>
+        <v>2397</v>
+      </c>
+      <c r="E67" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="68" spans="1:5" ht="15.75" customHeight="1">
       <c r="A68" s="45"/>
       <c r="B68" s="35"/>
       <c r="C68" s="35" t="s">
-        <v>2470</v>
+        <v>2398</v>
       </c>
       <c r="D68" s="35" t="s">
-        <v>1933</v>
-      </c>
-      <c r="E68" s="35"/>
+        <v>1930</v>
+      </c>
+      <c r="E68" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="69" spans="1:5" ht="15.75" customHeight="1">
       <c r="A69" s="45"/>
       <c r="B69" s="35"/>
       <c r="C69" s="35" t="s">
-        <v>2471</v>
+        <v>2399</v>
       </c>
       <c r="D69" s="35" t="s">
-        <v>1934</v>
-      </c>
-      <c r="E69" s="35"/>
+        <v>2650</v>
+      </c>
+      <c r="E69" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="70" spans="1:5" ht="15.75" customHeight="1">
       <c r="A70" s="45"/>
       <c r="B70" s="35"/>
       <c r="C70" s="35" t="s">
-        <v>2472</v>
+        <v>2400</v>
       </c>
       <c r="D70" s="35" t="s">
-        <v>1935</v>
-      </c>
-      <c r="E70" s="35"/>
+        <v>1931</v>
+      </c>
+      <c r="E70" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="71" spans="1:5" ht="15.75" customHeight="1">
       <c r="A71" s="45"/>
       <c r="B71" s="35"/>
       <c r="C71" s="35" t="s">
-        <v>2473</v>
+        <v>2401</v>
       </c>
       <c r="D71" s="35" t="s">
-        <v>1936</v>
-      </c>
-      <c r="E71" s="35"/>
+        <v>1932</v>
+      </c>
+      <c r="E71" s="35" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="72" spans="1:5" ht="15.75" customHeight="1">
       <c r="A72" s="45"/>
@@ -29012,10 +29281,10 @@
         <v>37</v>
       </c>
       <c r="C72" s="36" t="s">
-        <v>2474</v>
+        <v>2402</v>
       </c>
       <c r="D72" s="36" t="s">
-        <v>2475</v>
+        <v>2403</v>
       </c>
       <c r="E72" s="36" t="s">
         <v>1885</v>
@@ -29025,10 +29294,10 @@
       <c r="A73" s="45"/>
       <c r="B73" s="36"/>
       <c r="C73" s="36" t="s">
-        <v>2476</v>
+        <v>2404</v>
       </c>
       <c r="D73" s="36" t="s">
-        <v>2477</v>
+        <v>2405</v>
       </c>
       <c r="E73" s="36" t="s">
         <v>1885</v>
@@ -29038,10 +29307,10 @@
       <c r="A74" s="45"/>
       <c r="B74" s="36"/>
       <c r="C74" s="36" t="s">
-        <v>2478</v>
+        <v>2406</v>
       </c>
       <c r="D74" s="36" t="s">
-        <v>2479</v>
+        <v>2407</v>
       </c>
       <c r="E74" s="36" t="s">
         <v>1885</v>
@@ -29051,10 +29320,10 @@
       <c r="A75" s="45"/>
       <c r="B75" s="36"/>
       <c r="C75" s="36" t="s">
-        <v>2480</v>
+        <v>2408</v>
       </c>
       <c r="D75" s="36" t="s">
-        <v>2481</v>
+        <v>2409</v>
       </c>
       <c r="E75" s="36" t="s">
         <v>1885</v>
@@ -29064,10 +29333,10 @@
       <c r="A76" s="45"/>
       <c r="B76" s="36"/>
       <c r="C76" s="36" t="s">
-        <v>2482</v>
+        <v>2410</v>
       </c>
       <c r="D76" s="36" t="s">
-        <v>2483</v>
+        <v>2411</v>
       </c>
       <c r="E76" s="36" t="s">
         <v>1885</v>
@@ -29077,10 +29346,10 @@
       <c r="A77" s="45"/>
       <c r="B77" s="36"/>
       <c r="C77" s="36" t="s">
-        <v>2484</v>
+        <v>2412</v>
       </c>
       <c r="D77" s="36" t="s">
-        <v>2485</v>
+        <v>2413</v>
       </c>
       <c r="E77" s="36" t="s">
         <v>1885</v>
@@ -29090,10 +29359,10 @@
       <c r="A78" s="45"/>
       <c r="B78" s="36"/>
       <c r="C78" s="36" t="s">
-        <v>2486</v>
+        <v>2414</v>
       </c>
       <c r="D78" s="36" t="s">
-        <v>2487</v>
+        <v>2415</v>
       </c>
       <c r="E78" s="36" t="s">
         <v>1885</v>
@@ -29103,14 +29372,38 @@
       <c r="A79" s="45"/>
       <c r="B79" s="36"/>
       <c r="C79" s="36" t="s">
-        <v>2488</v>
+        <v>2416</v>
       </c>
       <c r="D79" s="36" t="s">
-        <v>2489</v>
+        <v>2417</v>
       </c>
       <c r="E79" s="36" t="s">
         <v>1885</v>
       </c>
+    </row>
+    <row r="158" spans="1:1" ht="15.75" customHeight="1">
+      <c r="A158" s="45"/>
+    </row>
+    <row r="159" spans="1:1" ht="15.75" customHeight="1">
+      <c r="A159" s="45"/>
+    </row>
+    <row r="160" spans="1:1" ht="15.75" customHeight="1">
+      <c r="A160" s="45"/>
+    </row>
+    <row r="161" spans="1:1" ht="15.75" customHeight="1">
+      <c r="A161" s="45"/>
+    </row>
+    <row r="162" spans="1:1" ht="15.75" customHeight="1">
+      <c r="A162" s="45"/>
+    </row>
+    <row r="163" spans="1:1" ht="15.75" customHeight="1">
+      <c r="A163" s="45"/>
+    </row>
+    <row r="164" spans="1:1" ht="15.75" customHeight="1">
+      <c r="A164" s="45"/>
+    </row>
+    <row r="165" spans="1:1" ht="15.75" customHeight="1">
+      <c r="A165" s="45"/>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
@@ -29123,7 +29416,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A2:Z31"/>
+  <dimension ref="A2:Z47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.83203125" customWidth="1"/>
@@ -29179,112 +29472,124 @@
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1">
       <c r="B3" s="45" t="s">
-        <v>2300</v>
+        <v>2263</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>1937</v>
+        <v>2651</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>2301</v>
+        <v>2652</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>1938</v>
-      </c>
-      <c r="F3" s="45"/>
+        <v>2653</v>
+      </c>
+      <c r="F3" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="G3" s="39"/>
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1">
       <c r="B4" s="45" t="s">
-        <v>2302</v>
+        <v>2264</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>2303</v>
+        <v>2654</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>2304</v>
+        <v>2655</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>2305</v>
-      </c>
-      <c r="F4" s="45"/>
+        <v>2656</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="G4" s="39"/>
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1">
       <c r="B5" s="45" t="s">
-        <v>2306</v>
+        <v>2268</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>2303</v>
+        <v>2657</v>
       </c>
       <c r="D5" s="45" t="s">
-        <v>2307</v>
+        <v>2658</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>2308</v>
-      </c>
-      <c r="F5" s="45"/>
+        <v>2659</v>
+      </c>
+      <c r="F5" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="G5" s="39"/>
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1">
       <c r="B6" s="45" t="s">
-        <v>2309</v>
+        <v>2271</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>2310</v>
+        <v>2265</v>
       </c>
       <c r="D6" s="45" t="s">
-        <v>2311</v>
+        <v>2266</v>
       </c>
       <c r="E6" s="45" t="s">
-        <v>2312</v>
-      </c>
-      <c r="F6" s="45"/>
+        <v>2267</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="G6" s="39"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1">
       <c r="B7" s="45" t="s">
-        <v>2313</v>
+        <v>2275</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>2314</v>
+        <v>2265</v>
       </c>
       <c r="D7" s="45" t="s">
-        <v>2315</v>
+        <v>2269</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>2316</v>
-      </c>
-      <c r="F7" s="45"/>
+        <v>2270</v>
+      </c>
+      <c r="F7" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="G7" s="39"/>
     </row>
     <row r="8" spans="1:26" ht="15.75" customHeight="1">
       <c r="B8" s="45" t="s">
-        <v>2317</v>
+        <v>2276</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>2318</v>
+        <v>2272</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>1939</v>
+        <v>2273</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>1940</v>
-      </c>
-      <c r="F8" s="45"/>
+        <v>2274</v>
+      </c>
+      <c r="F8" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="G8" s="39"/>
     </row>
     <row r="9" spans="1:26" ht="15.75" customHeight="1">
       <c r="B9" s="45" t="s">
-        <v>2319</v>
+        <v>2277</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>2320</v>
+        <v>2660</v>
       </c>
       <c r="D9" s="45" t="s">
-        <v>1941</v>
+        <v>2661</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>2321</v>
+        <v>2662</v>
       </c>
       <c r="F9" s="45" t="s">
         <v>1885</v>
@@ -29293,16 +29598,16 @@
     </row>
     <row r="10" spans="1:26" ht="15.75" customHeight="1">
       <c r="B10" s="45" t="s">
-        <v>2322</v>
+        <v>2280</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>2323</v>
+        <v>2663</v>
       </c>
       <c r="D10" s="45" t="s">
-        <v>2324</v>
+        <v>2664</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>2325</v>
+        <v>2665</v>
       </c>
       <c r="F10" s="45" t="s">
         <v>1885</v>
@@ -29311,196 +29616,208 @@
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1">
       <c r="B11" s="45" t="s">
-        <v>2326</v>
+        <v>2284</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>2327</v>
+        <v>2666</v>
       </c>
       <c r="D11" s="45" t="s">
-        <v>2328</v>
+        <v>2667</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>1942</v>
+        <v>2668</v>
       </c>
       <c r="F11" s="45" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="G11" s="39"/>
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1">
       <c r="B12" s="45" t="s">
-        <v>2329</v>
+        <v>2285</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>2330</v>
+        <v>2278</v>
       </c>
       <c r="D12" s="45" t="s">
-        <v>2331</v>
+        <v>1933</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>2332</v>
+        <v>2279</v>
       </c>
       <c r="F12" s="45" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="G12" s="39"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1">
       <c r="B13" s="45" t="s">
-        <v>2333</v>
+        <v>2286</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>2334</v>
+        <v>2281</v>
       </c>
       <c r="D13" s="45" t="s">
-        <v>2335</v>
+        <v>2282</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>2336</v>
+        <v>2283</v>
       </c>
       <c r="F13" s="45" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="G13" s="39"/>
     </row>
     <row r="14" spans="1:26" ht="15.75" customHeight="1">
       <c r="B14" s="45" t="s">
-        <v>2337</v>
+        <v>2287</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>2338</v>
+        <v>2669</v>
       </c>
       <c r="D14" s="45" t="s">
-        <v>1943</v>
+        <v>2670</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>1944</v>
-      </c>
-      <c r="F14" s="45"/>
+        <v>2671</v>
+      </c>
+      <c r="F14" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="G14" s="39"/>
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1">
       <c r="B15" s="45" t="s">
-        <v>2339</v>
+        <v>2288</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>2340</v>
+        <v>269</v>
       </c>
       <c r="D15" s="45" t="s">
-        <v>1945</v>
+        <v>2672</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>1946</v>
-      </c>
-      <c r="F15" s="45"/>
+        <v>2673</v>
+      </c>
+      <c r="F15" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="G15" s="39"/>
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1">
       <c r="B16" s="45" t="s">
-        <v>2341</v>
+        <v>2289</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>2342</v>
+        <v>281</v>
       </c>
       <c r="D16" s="45" t="s">
-        <v>1947</v>
+        <v>2674</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>1948</v>
-      </c>
-      <c r="F16" s="45"/>
+        <v>2675</v>
+      </c>
+      <c r="F16" s="45" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="17" spans="2:6" ht="15.75" customHeight="1">
       <c r="B17" s="45" t="s">
-        <v>2343</v>
+        <v>2290</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>199</v>
+        <v>262</v>
       </c>
       <c r="D17" s="45" t="s">
-        <v>2344</v>
+        <v>2676</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>1949</v>
-      </c>
-      <c r="F17" s="45"/>
+        <v>2677</v>
+      </c>
+      <c r="F17" s="45" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="18" spans="2:6" ht="15.75" customHeight="1">
       <c r="B18" s="45" t="s">
-        <v>2345</v>
+        <v>2292</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>2346</v>
+        <v>266</v>
       </c>
       <c r="D18" s="45" t="s">
-        <v>1950</v>
+        <v>2678</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>1951</v>
-      </c>
-      <c r="F18" s="45"/>
+        <v>2679</v>
+      </c>
+      <c r="F18" s="45" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="19" spans="2:6" ht="15.75" customHeight="1">
       <c r="B19" s="45" t="s">
-        <v>2347</v>
+        <v>2293</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>210</v>
+        <v>284</v>
       </c>
       <c r="D19" s="45" t="s">
-        <v>1952</v>
+        <v>2680</v>
       </c>
       <c r="E19" s="45" t="s">
-        <v>1953</v>
-      </c>
-      <c r="F19" s="45"/>
+        <v>2681</v>
+      </c>
+      <c r="F19" s="45" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="20" spans="2:6" ht="15.75" customHeight="1">
       <c r="B20" s="45" t="s">
-        <v>2348</v>
+        <v>2294</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>2349</v>
+        <v>2682</v>
       </c>
       <c r="D20" s="45" t="s">
-        <v>2350</v>
+        <v>2683</v>
       </c>
       <c r="E20" s="45" t="s">
-        <v>2351</v>
+        <v>2684</v>
       </c>
       <c r="F20" s="45" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="15.75" customHeight="1">
       <c r="B21" s="45" t="s">
-        <v>2352</v>
+        <v>2296</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>2353</v>
+        <v>178</v>
       </c>
       <c r="D21" s="45" t="s">
-        <v>2354</v>
+        <v>2685</v>
       </c>
       <c r="E21" s="45" t="s">
-        <v>2355</v>
+        <v>2686</v>
       </c>
       <c r="F21" s="45" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="15.75" customHeight="1">
       <c r="B22" s="45" t="s">
-        <v>2356</v>
+        <v>2298</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>2357</v>
+        <v>181</v>
       </c>
       <c r="D22" s="45" t="s">
-        <v>1954</v>
+        <v>2687</v>
       </c>
       <c r="E22" s="45" t="s">
-        <v>1955</v>
+        <v>2688</v>
       </c>
       <c r="F22" s="45" t="s">
         <v>1885</v>
@@ -29508,16 +29825,16 @@
     </row>
     <row r="23" spans="2:6" ht="15.75" customHeight="1">
       <c r="B23" s="45" t="s">
-        <v>2358</v>
+        <v>2300</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>2359</v>
+        <v>190</v>
       </c>
       <c r="D23" s="45" t="s">
-        <v>1956</v>
+        <v>2689</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>1957</v>
+        <v>2690</v>
       </c>
       <c r="F23" s="45" t="s">
         <v>1885</v>
@@ -29525,16 +29842,16 @@
     </row>
     <row r="24" spans="2:6" ht="15.75" customHeight="1">
       <c r="B24" s="45" t="s">
-        <v>2360</v>
+        <v>2302</v>
       </c>
       <c r="C24" s="45" t="s">
-        <v>2361</v>
+        <v>187</v>
       </c>
       <c r="D24" s="45" t="s">
-        <v>2362</v>
+        <v>2691</v>
       </c>
       <c r="E24" s="45" t="s">
-        <v>2363</v>
+        <v>2692</v>
       </c>
       <c r="F24" s="45" t="s">
         <v>1885</v>
@@ -29542,16 +29859,16 @@
     </row>
     <row r="25" spans="2:6" ht="15.75" customHeight="1">
       <c r="B25" s="45" t="s">
-        <v>2364</v>
+        <v>2306</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>2365</v>
+        <v>184</v>
       </c>
       <c r="D25" s="45" t="s">
-        <v>2366</v>
+        <v>2693</v>
       </c>
       <c r="E25" s="45" t="s">
-        <v>1958</v>
+        <v>2694</v>
       </c>
       <c r="F25" s="45" t="s">
         <v>1885</v>
@@ -29559,16 +29876,16 @@
     </row>
     <row r="26" spans="2:6" ht="15.75" customHeight="1">
       <c r="B26" s="45" t="s">
-        <v>2367</v>
+        <v>2309</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>343</v>
+        <v>193</v>
       </c>
       <c r="D26" s="45" t="s">
-        <v>2368</v>
+        <v>2695</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>2369</v>
+        <v>2696</v>
       </c>
       <c r="F26" s="45" t="s">
         <v>1885</v>
@@ -29576,16 +29893,16 @@
     </row>
     <row r="27" spans="2:6" ht="15.75" customHeight="1">
       <c r="B27" s="45" t="s">
-        <v>2370</v>
+        <v>2311</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>2371</v>
+        <v>196</v>
       </c>
       <c r="D27" s="45" t="s">
-        <v>2372</v>
+        <v>2697</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>2373</v>
+        <v>2698</v>
       </c>
       <c r="F27" s="45" t="s">
         <v>1885</v>
@@ -29593,16 +29910,16 @@
     </row>
     <row r="28" spans="2:6" ht="15.75" customHeight="1">
       <c r="B28" s="45" t="s">
-        <v>2374</v>
+        <v>2313</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>2375</v>
+        <v>199</v>
       </c>
       <c r="D28" s="45" t="s">
-        <v>2376</v>
+        <v>2291</v>
       </c>
       <c r="E28" s="45" t="s">
-        <v>2377</v>
+        <v>1934</v>
       </c>
       <c r="F28" s="45" t="s">
         <v>1885</v>
@@ -29610,16 +29927,16 @@
     </row>
     <row r="29" spans="2:6" ht="15.75" customHeight="1">
       <c r="B29" s="45" t="s">
-        <v>2378</v>
+        <v>2314</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>2379</v>
+        <v>202</v>
       </c>
       <c r="D29" s="45" t="s">
-        <v>2380</v>
+        <v>2699</v>
       </c>
       <c r="E29" s="45" t="s">
-        <v>2381</v>
+        <v>2700</v>
       </c>
       <c r="F29" s="45" t="s">
         <v>1885</v>
@@ -29627,16 +29944,16 @@
     </row>
     <row r="30" spans="2:6" ht="15.75" customHeight="1">
       <c r="B30" s="45" t="s">
-        <v>2382</v>
+        <v>2315</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>2383</v>
+        <v>205</v>
       </c>
       <c r="D30" s="45" t="s">
-        <v>2384</v>
+        <v>2701</v>
       </c>
       <c r="E30" s="45" t="s">
-        <v>2385</v>
+        <v>2702</v>
       </c>
       <c r="F30" s="45" t="s">
         <v>1885</v>
@@ -29644,18 +29961,290 @@
     </row>
     <row r="31" spans="2:6" ht="15.75" customHeight="1">
       <c r="B31" s="45" t="s">
-        <v>2386</v>
+        <v>2318</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>2387</v>
+        <v>205</v>
       </c>
       <c r="D31" s="45" t="s">
-        <v>2388</v>
+        <v>2703</v>
       </c>
       <c r="E31" s="45" t="s">
-        <v>2389</v>
+        <v>2704</v>
       </c>
       <c r="F31" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B32" s="45" t="s">
+        <v>2705</v>
+      </c>
+      <c r="C32" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="D32" s="45" t="s">
+        <v>2706</v>
+      </c>
+      <c r="E32" s="45" t="s">
+        <v>2707</v>
+      </c>
+      <c r="F32" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B33" s="45" t="s">
+        <v>2708</v>
+      </c>
+      <c r="C33" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="D33" s="45" t="s">
+        <v>2709</v>
+      </c>
+      <c r="E33" s="45" t="s">
+        <v>2710</v>
+      </c>
+      <c r="F33" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B34" s="45" t="s">
+        <v>2711</v>
+      </c>
+      <c r="C34" s="45" t="s">
+        <v>2295</v>
+      </c>
+      <c r="D34" s="45" t="s">
+        <v>2712</v>
+      </c>
+      <c r="E34" s="45" t="s">
+        <v>2713</v>
+      </c>
+      <c r="F34" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B35" s="45" t="s">
+        <v>2714</v>
+      </c>
+      <c r="C35" s="45" t="s">
+        <v>306</v>
+      </c>
+      <c r="D35" s="45" t="s">
+        <v>2715</v>
+      </c>
+      <c r="E35" s="45" t="s">
+        <v>2716</v>
+      </c>
+      <c r="F35" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B36" s="45" t="s">
+        <v>2717</v>
+      </c>
+      <c r="C36" s="45" t="s">
+        <v>309</v>
+      </c>
+      <c r="D36" s="45" t="s">
+        <v>2718</v>
+      </c>
+      <c r="E36" s="45" t="s">
+        <v>2719</v>
+      </c>
+      <c r="F36" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B37" s="45" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C37" s="45" t="s">
+        <v>2721</v>
+      </c>
+      <c r="D37" s="45" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E37" s="45" t="s">
+        <v>2722</v>
+      </c>
+      <c r="F37" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B38" s="45" t="s">
+        <v>2723</v>
+      </c>
+      <c r="C38" s="45" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D38" s="45" t="s">
+        <v>1935</v>
+      </c>
+      <c r="E38" s="45" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F38" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B39" s="45" t="s">
+        <v>2724</v>
+      </c>
+      <c r="C39" s="45" t="s">
+        <v>2301</v>
+      </c>
+      <c r="D39" s="45" t="s">
+        <v>1937</v>
+      </c>
+      <c r="E39" s="45" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F39" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B40" s="45" t="s">
+        <v>2725</v>
+      </c>
+      <c r="C40" s="45" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D40" s="45" t="s">
+        <v>2304</v>
+      </c>
+      <c r="E40" s="45" t="s">
+        <v>2305</v>
+      </c>
+      <c r="F40" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B41" s="45" t="s">
+        <v>2726</v>
+      </c>
+      <c r="C41" s="45" t="s">
+        <v>2307</v>
+      </c>
+      <c r="D41" s="45" t="s">
+        <v>2308</v>
+      </c>
+      <c r="E41" s="45" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F41" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B42" s="45" t="s">
+        <v>2727</v>
+      </c>
+      <c r="C42" s="45" t="s">
+        <v>343</v>
+      </c>
+      <c r="D42" s="45" t="s">
+        <v>2310</v>
+      </c>
+      <c r="E42" s="45" t="s">
+        <v>2728</v>
+      </c>
+      <c r="F42" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B43" s="45" t="s">
+        <v>2729</v>
+      </c>
+      <c r="C43" s="45" t="s">
+        <v>2312</v>
+      </c>
+      <c r="D43" s="45" t="s">
+        <v>2730</v>
+      </c>
+      <c r="E43" s="45" t="s">
+        <v>2731</v>
+      </c>
+      <c r="F43" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B44" s="45" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C44" s="45" t="s">
+        <v>2733</v>
+      </c>
+      <c r="D44" s="45" t="s">
+        <v>2734</v>
+      </c>
+      <c r="E44" s="45" t="s">
+        <v>2735</v>
+      </c>
+      <c r="F44" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B45" s="45" t="s">
+        <v>2736</v>
+      </c>
+      <c r="C45" s="45" t="s">
+        <v>2737</v>
+      </c>
+      <c r="D45" s="45" t="s">
+        <v>2738</v>
+      </c>
+      <c r="E45" s="45" t="s">
+        <v>2739</v>
+      </c>
+      <c r="F45" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B46" s="45" t="s">
+        <v>2740</v>
+      </c>
+      <c r="C46" s="45" t="s">
+        <v>2741</v>
+      </c>
+      <c r="D46" s="45" t="s">
+        <v>2316</v>
+      </c>
+      <c r="E46" s="45" t="s">
+        <v>2317</v>
+      </c>
+      <c r="F46" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" ht="15.75" customHeight="1">
+      <c r="B47" s="45" t="s">
+        <v>2742</v>
+      </c>
+      <c r="C47" s="45" t="s">
+        <v>2743</v>
+      </c>
+      <c r="D47" s="45" t="s">
+        <v>2319</v>
+      </c>
+      <c r="E47" s="45" t="s">
+        <v>2320</v>
+      </c>
+      <c r="F47" s="45" t="s">
         <v>1885</v>
       </c>
     </row>
@@ -29670,7 +30259,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="3" max="3" width="83.5" customWidth="1"/>
@@ -29699,232 +30288,270 @@
     </row>
     <row r="3" spans="1:6" ht="14">
       <c r="B3" s="45" t="s">
-        <v>2218</v>
+        <v>2199</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>2219</v>
-      </c>
-      <c r="D3" s="45"/>
+        <v>2200</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E3" s="4"/>
       <c r="F3" s="39"/>
     </row>
     <row r="4" spans="1:6" ht="14">
       <c r="B4" s="45" t="s">
-        <v>2220</v>
+        <v>2201</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>2221</v>
-      </c>
-      <c r="D4" s="45"/>
+        <v>2202</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E4" s="4"/>
       <c r="F4" s="39"/>
     </row>
     <row r="5" spans="1:6" ht="14">
       <c r="B5" s="45" t="s">
-        <v>2222</v>
+        <v>2203</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>2223</v>
-      </c>
-      <c r="D5" s="45"/>
+        <v>2744</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E5" s="4"/>
       <c r="F5" s="39"/>
     </row>
     <row r="6" spans="1:6" ht="14">
       <c r="B6" s="45" t="s">
-        <v>2224</v>
+        <v>2204</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>2225</v>
-      </c>
-      <c r="D6" s="45"/>
+        <v>2745</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E6" s="4"/>
       <c r="F6" s="39"/>
     </row>
     <row r="7" spans="1:6" ht="14">
       <c r="B7" s="45" t="s">
-        <v>2226</v>
+        <v>2205</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>2227</v>
-      </c>
-      <c r="D7" s="45"/>
+        <v>2746</v>
+      </c>
+      <c r="D7" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E7" s="4"/>
       <c r="F7" s="39"/>
     </row>
     <row r="8" spans="1:6" ht="14">
       <c r="B8" s="45" t="s">
-        <v>2228</v>
+        <v>2206</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>2229</v>
-      </c>
-      <c r="D8" s="45"/>
+        <v>2747</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E8" s="4"/>
       <c r="F8" s="39"/>
     </row>
     <row r="9" spans="1:6" ht="14">
       <c r="B9" s="45" t="s">
-        <v>2230</v>
+        <v>2207</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>2231</v>
-      </c>
-      <c r="D9" s="45"/>
+        <v>2748</v>
+      </c>
+      <c r="D9" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E9" s="4"/>
       <c r="F9" s="39"/>
     </row>
     <row r="10" spans="1:6" ht="15">
       <c r="B10" s="45" t="s">
-        <v>2232</v>
+        <v>2208</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>2233</v>
-      </c>
-      <c r="D10" s="45"/>
+        <v>2209</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E10" s="44"/>
       <c r="F10" s="39"/>
     </row>
     <row r="11" spans="1:6" ht="15">
       <c r="B11" s="45" t="s">
-        <v>2234</v>
+        <v>2210</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>2235</v>
-      </c>
-      <c r="D11" s="45"/>
+        <v>2211</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E11" s="44"/>
       <c r="F11" s="39"/>
     </row>
     <row r="12" spans="1:6" ht="28">
       <c r="B12" s="45" t="s">
-        <v>2236</v>
+        <v>2212</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>2237</v>
-      </c>
-      <c r="D12" s="45"/>
+        <v>2749</v>
+      </c>
+      <c r="D12" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E12" s="44"/>
       <c r="F12" s="39"/>
     </row>
     <row r="13" spans="1:6" ht="15">
       <c r="B13" s="45" t="s">
-        <v>2238</v>
+        <v>2213</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>2239</v>
-      </c>
-      <c r="D13" s="45"/>
+        <v>2214</v>
+      </c>
+      <c r="D13" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E13" s="44"/>
       <c r="F13" s="39"/>
     </row>
     <row r="14" spans="1:6" ht="14">
       <c r="B14" s="45" t="s">
-        <v>2240</v>
+        <v>2215</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>2241</v>
-      </c>
-      <c r="D14" s="45"/>
+        <v>2216</v>
+      </c>
+      <c r="D14" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E14" s="43"/>
       <c r="F14" s="39"/>
     </row>
     <row r="15" spans="1:6" ht="15">
       <c r="B15" s="45" t="s">
-        <v>2242</v>
+        <v>2217</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D15" s="45"/>
+        <v>2218</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E15" s="44"/>
       <c r="F15" s="39"/>
     </row>
     <row r="16" spans="1:6" ht="14">
       <c r="B16" s="45" t="s">
-        <v>2244</v>
+        <v>2219</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>2245</v>
-      </c>
-      <c r="D16" s="45"/>
+        <v>2220</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E16" s="43"/>
       <c r="F16" s="39"/>
     </row>
     <row r="17" spans="2:6" ht="15">
       <c r="B17" s="45" t="s">
-        <v>2246</v>
+        <v>2221</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>2247</v>
-      </c>
-      <c r="D17" s="45"/>
+        <v>2222</v>
+      </c>
+      <c r="D17" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E17" s="44"/>
       <c r="F17" s="39"/>
     </row>
     <row r="18" spans="2:6" ht="28">
       <c r="B18" s="45" t="s">
-        <v>2248</v>
+        <v>2223</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>2249</v>
-      </c>
-      <c r="D18" s="45"/>
+        <v>2224</v>
+      </c>
+      <c r="D18" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E18" s="43"/>
       <c r="F18" s="39"/>
     </row>
     <row r="19" spans="2:6" ht="28">
       <c r="B19" s="45" t="s">
-        <v>2250</v>
+        <v>2225</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>2251</v>
-      </c>
-      <c r="D19" s="45"/>
+        <v>2226</v>
+      </c>
+      <c r="D19" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E19" s="43"/>
       <c r="F19" s="39"/>
     </row>
     <row r="20" spans="2:6" ht="28">
       <c r="B20" s="45" t="s">
-        <v>2252</v>
+        <v>2227</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>2253</v>
+        <v>2750</v>
       </c>
       <c r="D20" s="45" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="E20" s="43"/>
       <c r="F20" s="39"/>
     </row>
-    <row r="21" spans="2:6" ht="14">
+    <row r="21" spans="2:6" ht="28">
       <c r="B21" s="45" t="s">
-        <v>2254</v>
+        <v>2228</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>2255</v>
-      </c>
-      <c r="D21" s="45"/>
+        <v>2751</v>
+      </c>
+      <c r="D21" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E21" s="43"/>
       <c r="F21" s="39"/>
     </row>
     <row r="22" spans="2:6" ht="14">
       <c r="B22" s="45" t="s">
-        <v>2256</v>
+        <v>2230</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>2257</v>
-      </c>
-      <c r="D22" s="45"/>
+        <v>2229</v>
+      </c>
+      <c r="D22" s="45" t="s">
+        <v>1885</v>
+      </c>
       <c r="E22" s="4"/>
       <c r="F22" s="39"/>
     </row>
     <row r="23" spans="2:6" ht="15.75" customHeight="1">
       <c r="B23" s="45" t="s">
-        <v>2258</v>
+        <v>2232</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>2259</v>
+        <v>2231</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>1885</v>
@@ -29932,10 +30559,10 @@
     </row>
     <row r="24" spans="2:6" ht="28">
       <c r="B24" s="45" t="s">
-        <v>2260</v>
+        <v>2233</v>
       </c>
       <c r="C24" s="45" t="s">
-        <v>2261</v>
+        <v>2752</v>
       </c>
       <c r="D24" s="45" t="s">
         <v>1885</v>
@@ -29943,10 +30570,10 @@
     </row>
     <row r="25" spans="2:6" ht="28">
       <c r="B25" s="45" t="s">
-        <v>2262</v>
+        <v>2234</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>2263</v>
+        <v>2753</v>
       </c>
       <c r="D25" s="45" t="s">
         <v>1885</v>
@@ -29954,21 +30581,21 @@
     </row>
     <row r="26" spans="2:6" ht="15.75" customHeight="1">
       <c r="B26" s="45" t="s">
-        <v>2264</v>
+        <v>2236</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>2265</v>
+        <v>2235</v>
       </c>
       <c r="D26" s="45" t="s">
         <v>1885</v>
       </c>
     </row>
-    <row r="27" spans="2:6" ht="14">
+    <row r="27" spans="2:6" ht="28">
       <c r="B27" s="45" t="s">
-        <v>2266</v>
+        <v>2238</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>2267</v>
+        <v>2237</v>
       </c>
       <c r="D27" s="45" t="s">
         <v>1885</v>
@@ -29976,98 +30603,98 @@
     </row>
     <row r="28" spans="2:6" ht="15.75" customHeight="1">
       <c r="B28" s="45" t="s">
-        <v>2268</v>
+        <v>2240</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>2269</v>
+        <v>2239</v>
       </c>
       <c r="D28" s="45" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="15.75" customHeight="1">
       <c r="B29" s="45" t="s">
-        <v>2270</v>
+        <v>2241</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>2271</v>
+        <v>2754</v>
       </c>
       <c r="D29" s="45" t="s">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" ht="28">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" ht="14">
       <c r="B30" s="45" t="s">
-        <v>2272</v>
+        <v>2242</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>2273</v>
+        <v>2755</v>
       </c>
       <c r="D30" s="45" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="31" spans="2:6" ht="15.75" customHeight="1">
       <c r="B31" s="45" t="s">
-        <v>2274</v>
+        <v>2243</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>2275</v>
+        <v>2756</v>
       </c>
       <c r="D31" s="45" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="32" spans="2:6" ht="15.75" customHeight="1">
       <c r="B32" s="45" t="s">
-        <v>2276</v>
+        <v>2244</v>
       </c>
       <c r="C32" s="45" t="s">
-        <v>2277</v>
+        <v>2757</v>
       </c>
       <c r="D32" s="45" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="33" spans="2:4" ht="15.75" customHeight="1">
       <c r="B33" s="45" t="s">
-        <v>2278</v>
+        <v>2245</v>
       </c>
       <c r="C33" s="45" t="s">
-        <v>2279</v>
+        <v>2758</v>
       </c>
       <c r="D33" s="45" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="34" spans="2:4" ht="15.75" customHeight="1">
       <c r="B34" s="45" t="s">
-        <v>2280</v>
+        <v>2246</v>
       </c>
       <c r="C34" s="45" t="s">
-        <v>2281</v>
+        <v>2759</v>
       </c>
       <c r="D34" s="45" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="35" spans="2:4" ht="15.75" customHeight="1">
       <c r="B35" s="45" t="s">
-        <v>2282</v>
+        <v>2247</v>
       </c>
       <c r="C35" s="45" t="s">
-        <v>2283</v>
+        <v>2760</v>
       </c>
       <c r="D35" s="45" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="36" spans="2:4" ht="15.75" customHeight="1">
       <c r="B36" s="45" t="s">
-        <v>2284</v>
+        <v>2248</v>
       </c>
       <c r="C36" s="45" t="s">
-        <v>2285</v>
+        <v>2761</v>
       </c>
       <c r="D36" s="45" t="s">
         <v>1885</v>
@@ -30075,10 +30702,10 @@
     </row>
     <row r="37" spans="2:4" ht="15.75" customHeight="1">
       <c r="B37" s="45" t="s">
-        <v>2286</v>
+        <v>2250</v>
       </c>
       <c r="C37" s="45" t="s">
-        <v>2287</v>
+        <v>2762</v>
       </c>
       <c r="D37" s="45" t="s">
         <v>1885</v>
@@ -30086,10 +30713,10 @@
     </row>
     <row r="38" spans="2:4" ht="15.75" customHeight="1">
       <c r="B38" s="45" t="s">
-        <v>2288</v>
+        <v>2252</v>
       </c>
       <c r="C38" s="45" t="s">
-        <v>2289</v>
+        <v>2763</v>
       </c>
       <c r="D38" s="45" t="s">
         <v>1885</v>
@@ -30097,10 +30724,10 @@
     </row>
     <row r="39" spans="2:4" ht="15.75" customHeight="1">
       <c r="B39" s="45" t="s">
-        <v>2290</v>
+        <v>2254</v>
       </c>
       <c r="C39" s="45" t="s">
-        <v>2291</v>
+        <v>2764</v>
       </c>
       <c r="D39" s="45" t="s">
         <v>1885</v>
@@ -30108,10 +30735,10 @@
     </row>
     <row r="40" spans="2:4" ht="15.75" customHeight="1">
       <c r="B40" s="45" t="s">
-        <v>2292</v>
+        <v>2256</v>
       </c>
       <c r="C40" s="45" t="s">
-        <v>2293</v>
+        <v>2765</v>
       </c>
       <c r="D40" s="45" t="s">
         <v>1885</v>
@@ -30119,10 +30746,10 @@
     </row>
     <row r="41" spans="2:4" ht="15.75" customHeight="1">
       <c r="B41" s="45" t="s">
-        <v>2294</v>
+        <v>2257</v>
       </c>
       <c r="C41" s="45" t="s">
-        <v>2295</v>
+        <v>2249</v>
       </c>
       <c r="D41" s="45" t="s">
         <v>1885</v>
@@ -30130,21 +30757,80 @@
     </row>
     <row r="42" spans="2:4" ht="15.75" customHeight="1">
       <c r="B42" s="45" t="s">
-        <v>2296</v>
+        <v>2259</v>
       </c>
       <c r="C42" s="45" t="s">
-        <v>2297</v>
-      </c>
-      <c r="D42" s="45"/>
+        <v>2251</v>
+      </c>
+      <c r="D42" s="45" t="s">
+        <v>1885</v>
+      </c>
     </row>
     <row r="43" spans="2:4" ht="15.75" customHeight="1">
       <c r="B43" s="45" t="s">
-        <v>2298</v>
+        <v>2261</v>
       </c>
       <c r="C43" s="45" t="s">
-        <v>2299</v>
-      </c>
-      <c r="D43" s="45"/>
+        <v>2253</v>
+      </c>
+      <c r="D43" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" ht="15.75" customHeight="1">
+      <c r="B44" s="45" t="s">
+        <v>2766</v>
+      </c>
+      <c r="C44" s="45" t="s">
+        <v>2255</v>
+      </c>
+      <c r="D44" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" ht="15.75" customHeight="1">
+      <c r="B45" s="45" t="s">
+        <v>2767</v>
+      </c>
+      <c r="C45" s="45" t="s">
+        <v>2768</v>
+      </c>
+      <c r="D45" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" ht="15.75" customHeight="1">
+      <c r="B46" s="45" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C46" s="45" t="s">
+        <v>2258</v>
+      </c>
+      <c r="D46" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" ht="15.75" customHeight="1">
+      <c r="B47" s="45" t="s">
+        <v>2770</v>
+      </c>
+      <c r="C47" s="45" t="s">
+        <v>2260</v>
+      </c>
+      <c r="D47" s="45" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" ht="15.75" customHeight="1">
+      <c r="B48" s="45" t="s">
+        <v>2771</v>
+      </c>
+      <c r="C48" s="45" t="s">
+        <v>2262</v>
+      </c>
+      <c r="D48" s="45" t="s">
+        <v>1885</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
@@ -30171,7 +30857,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="36">
       <c r="A1" s="77" t="s">
-        <v>2116</v>
+        <v>2097</v>
       </c>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -30199,7 +30885,7 @@
     </row>
     <row r="3" spans="1:11" ht="15">
       <c r="A3" s="76" t="s">
-        <v>2115</v>
+        <v>2096</v>
       </c>
       <c r="B3" s="76"/>
       <c r="C3" s="76"/>
@@ -30214,7 +30900,7 @@
     </row>
     <row r="4" spans="1:11" ht="30">
       <c r="A4" s="76" t="s">
-        <v>2114</v>
+        <v>2095</v>
       </c>
       <c r="B4" s="76"/>
       <c r="C4" s="76"/>
@@ -30229,7 +30915,7 @@
     </row>
     <row r="5" spans="1:11" ht="15">
       <c r="A5" s="76" t="s">
-        <v>2113</v>
+        <v>2094</v>
       </c>
       <c r="B5" s="76"/>
       <c r="C5" s="76"/>
@@ -30244,7 +30930,7 @@
     </row>
     <row r="6" spans="1:11" ht="15">
       <c r="A6" s="76" t="s">
-        <v>2112</v>
+        <v>2093</v>
       </c>
       <c r="B6" s="76"/>
       <c r="C6" s="76"/>
@@ -30259,7 +30945,7 @@
     </row>
     <row r="7" spans="1:11" ht="15">
       <c r="A7" s="76" t="s">
-        <v>2033</v>
+        <v>2014</v>
       </c>
       <c r="B7" s="76"/>
       <c r="C7" s="76"/>
@@ -30274,7 +30960,7 @@
     </row>
     <row r="8" spans="1:11" ht="15">
       <c r="A8" s="76" t="s">
-        <v>2032</v>
+        <v>2013</v>
       </c>
       <c r="B8" s="76"/>
       <c r="C8" s="76"/>
@@ -30289,7 +30975,7 @@
     </row>
     <row r="9" spans="1:11" ht="15">
       <c r="A9" s="76" t="s">
-        <v>2031</v>
+        <v>2012</v>
       </c>
       <c r="B9" s="76"/>
       <c r="C9" s="76"/>
@@ -30304,7 +30990,7 @@
     </row>
     <row r="10" spans="1:11" ht="30">
       <c r="A10" s="76" t="s">
-        <v>2030</v>
+        <v>2011</v>
       </c>
       <c r="B10" s="76"/>
       <c r="C10" s="76"/>
@@ -30345,7 +31031,7 @@
     </row>
     <row r="13" spans="1:11" ht="18">
       <c r="A13" s="97" t="s">
-        <v>2111</v>
+        <v>2092</v>
       </c>
       <c r="B13" s="45"/>
       <c r="C13" s="45"/>
@@ -30373,13 +31059,13 @@
     </row>
     <row r="15" spans="1:11" ht="18">
       <c r="A15" s="52" t="s">
-        <v>1960</v>
+        <v>1941</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>2110</v>
+        <v>2091</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>2109</v>
+        <v>2090</v>
       </c>
       <c r="D15" s="45"/>
       <c r="E15" s="45"/>
@@ -30392,13 +31078,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="45" t="s">
-        <v>2108</v>
+        <v>2089</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>2107</v>
+        <v>2088</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>2106</v>
+        <v>2087</v>
       </c>
       <c r="D16" s="45"/>
       <c r="E16" s="45"/>
@@ -30411,13 +31097,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="45" t="s">
-        <v>2105</v>
+        <v>2086</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>2104</v>
+        <v>2085</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>2103</v>
+        <v>2084</v>
       </c>
       <c r="D17" s="45"/>
       <c r="E17" s="45"/>
@@ -30430,13 +31116,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="45" t="s">
-        <v>2102</v>
+        <v>2083</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>2101</v>
+        <v>2082</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>2100</v>
+        <v>2081</v>
       </c>
       <c r="D18" s="45"/>
       <c r="E18" s="45"/>
@@ -30475,7 +31161,7 @@
     </row>
     <row r="21" spans="1:11" ht="18">
       <c r="A21" s="97" t="s">
-        <v>2099</v>
+        <v>2080</v>
       </c>
       <c r="B21" s="45"/>
       <c r="C21" s="45"/>
@@ -30503,317 +31189,317 @@
     </row>
     <row r="23" spans="1:11" ht="18">
       <c r="A23" s="52" t="s">
-        <v>2098</v>
+        <v>2079</v>
       </c>
       <c r="B23" s="52" t="s">
-        <v>2097</v>
+        <v>2078</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>2096</v>
+        <v>2077</v>
       </c>
       <c r="D23" s="52" t="s">
-        <v>2095</v>
+        <v>2076</v>
       </c>
       <c r="E23" s="52" t="s">
-        <v>2094</v>
+        <v>2075</v>
       </c>
       <c r="F23" s="52" t="s">
-        <v>2093</v>
+        <v>2074</v>
       </c>
       <c r="G23" s="52" t="s">
-        <v>2092</v>
+        <v>2073</v>
       </c>
       <c r="H23" s="52" t="s">
-        <v>2091</v>
+        <v>2072</v>
       </c>
       <c r="I23" s="52" t="s">
-        <v>2090</v>
+        <v>2071</v>
       </c>
       <c r="J23" s="52" t="s">
-        <v>2089</v>
+        <v>2070</v>
       </c>
       <c r="K23" s="52" t="s">
-        <v>2088</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="42">
       <c r="A24" s="45" t="s">
-        <v>2087</v>
+        <v>2068</v>
       </c>
       <c r="B24" s="45" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="45" t="s">
-        <v>2086</v>
+        <v>2067</v>
       </c>
       <c r="D24" s="45" t="s">
-        <v>2085</v>
+        <v>2066</v>
       </c>
       <c r="E24" s="45" t="s">
-        <v>2042</v>
+        <v>2023</v>
       </c>
       <c r="F24" s="45" t="s">
-        <v>2067</v>
+        <v>2048</v>
       </c>
       <c r="G24" s="45" t="s">
-        <v>2040</v>
+        <v>2021</v>
       </c>
       <c r="H24" s="45" t="s">
-        <v>2066</v>
+        <v>2047</v>
       </c>
       <c r="I24" s="45" t="s">
-        <v>2084</v>
+        <v>2065</v>
       </c>
       <c r="J24" s="45" t="s">
-        <v>2083</v>
+        <v>2064</v>
       </c>
       <c r="K24" s="45" t="s">
-        <v>2657</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="28">
       <c r="A25" s="45" t="s">
-        <v>2082</v>
+        <v>2063</v>
       </c>
       <c r="B25" s="45" t="s">
-        <v>2081</v>
+        <v>2062</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>2080</v>
+        <v>2061</v>
       </c>
       <c r="D25" s="45" t="s">
-        <v>2079</v>
+        <v>2060</v>
       </c>
       <c r="E25" s="45" t="s">
-        <v>2050</v>
+        <v>2031</v>
       </c>
       <c r="F25" s="45" t="s">
-        <v>2041</v>
+        <v>2022</v>
       </c>
       <c r="G25" s="45" t="s">
-        <v>2078</v>
+        <v>2059</v>
       </c>
       <c r="H25" s="45" t="s">
-        <v>2062</v>
+        <v>2043</v>
       </c>
       <c r="I25" s="45" t="s">
-        <v>2077</v>
+        <v>2058</v>
       </c>
       <c r="J25" s="45" t="s">
-        <v>2076</v>
+        <v>2057</v>
       </c>
       <c r="K25" s="45" t="s">
-        <v>2658</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="28">
       <c r="A26" s="45" t="s">
-        <v>2075</v>
+        <v>2056</v>
       </c>
       <c r="B26" s="45" t="s">
-        <v>2659</v>
+        <v>2587</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>2074</v>
+        <v>2055</v>
       </c>
       <c r="D26" s="45" t="s">
-        <v>2073</v>
+        <v>2054</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>2050</v>
+        <v>2031</v>
       </c>
       <c r="F26" s="45" t="s">
-        <v>2041</v>
+        <v>2022</v>
       </c>
       <c r="G26" s="45" t="s">
-        <v>2040</v>
+        <v>2021</v>
       </c>
       <c r="H26" s="45" t="s">
-        <v>2062</v>
+        <v>2043</v>
       </c>
       <c r="I26" s="45" t="s">
-        <v>2072</v>
+        <v>2053</v>
       </c>
       <c r="J26" s="45" t="s">
-        <v>2071</v>
+        <v>2052</v>
       </c>
       <c r="K26" s="45" t="s">
-        <v>2660</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="28">
       <c r="A27" s="45" t="s">
-        <v>2070</v>
+        <v>2051</v>
       </c>
       <c r="B27" s="45" t="s">
-        <v>2661</v>
+        <v>2589</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>2069</v>
+        <v>2050</v>
       </c>
       <c r="D27" s="45" t="s">
-        <v>2068</v>
+        <v>2049</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>2042</v>
+        <v>2023</v>
       </c>
       <c r="F27" s="45" t="s">
-        <v>2067</v>
+        <v>2048</v>
       </c>
       <c r="G27" s="45" t="s">
-        <v>2040</v>
+        <v>2021</v>
       </c>
       <c r="H27" s="45" t="s">
-        <v>2066</v>
+        <v>2047</v>
       </c>
       <c r="I27" s="45" t="s">
-        <v>2065</v>
+        <v>2046</v>
       </c>
       <c r="J27" s="45" t="s">
-        <v>2064</v>
+        <v>2045</v>
       </c>
       <c r="K27" s="45" t="s">
-        <v>2662</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="28">
       <c r="A28" s="45" t="s">
-        <v>2063</v>
+        <v>2044</v>
       </c>
       <c r="B28" s="45" t="s">
-        <v>2663</v>
+        <v>2591</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>2664</v>
+        <v>2592</v>
       </c>
       <c r="D28" s="45" t="s">
-        <v>2665</v>
+        <v>2593</v>
       </c>
       <c r="E28" s="45" t="s">
-        <v>2050</v>
+        <v>2031</v>
       </c>
       <c r="F28" s="45" t="s">
-        <v>2041</v>
+        <v>2022</v>
       </c>
       <c r="G28" s="45" t="s">
-        <v>2040</v>
+        <v>2021</v>
       </c>
       <c r="H28" s="45" t="s">
-        <v>2062</v>
+        <v>2043</v>
       </c>
       <c r="I28" s="45" t="s">
-        <v>2666</v>
+        <v>2594</v>
       </c>
       <c r="J28" s="45" t="s">
-        <v>2061</v>
+        <v>2042</v>
       </c>
       <c r="K28" s="45" t="s">
-        <v>2667</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="28">
       <c r="A29" s="45" t="s">
-        <v>2060</v>
+        <v>2041</v>
       </c>
       <c r="B29" s="45" t="s">
-        <v>2059</v>
+        <v>2040</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>2058</v>
+        <v>2039</v>
       </c>
       <c r="D29" s="45" t="s">
-        <v>2057</v>
+        <v>2038</v>
       </c>
       <c r="E29" s="45" t="s">
-        <v>2050</v>
+        <v>2031</v>
       </c>
       <c r="F29" s="45" t="s">
-        <v>2041</v>
+        <v>2022</v>
       </c>
       <c r="G29" s="45" t="s">
-        <v>2040</v>
+        <v>2021</v>
       </c>
       <c r="H29" s="45" t="s">
-        <v>2049</v>
+        <v>2030</v>
       </c>
       <c r="I29" s="45" t="s">
-        <v>2056</v>
+        <v>2037</v>
       </c>
       <c r="J29" s="45" t="s">
-        <v>2055</v>
+        <v>2036</v>
       </c>
       <c r="K29" s="45" t="s">
-        <v>2668</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="28">
       <c r="A30" s="45" t="s">
-        <v>2054</v>
+        <v>2035</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>2053</v>
+        <v>2034</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>2052</v>
+        <v>2033</v>
       </c>
       <c r="D30" s="45" t="s">
-        <v>2051</v>
+        <v>2032</v>
       </c>
       <c r="E30" s="45" t="s">
-        <v>2050</v>
+        <v>2031</v>
       </c>
       <c r="F30" s="45" t="s">
-        <v>2041</v>
+        <v>2022</v>
       </c>
       <c r="G30" s="45" t="s">
-        <v>2040</v>
+        <v>2021</v>
       </c>
       <c r="H30" s="45" t="s">
-        <v>2049</v>
+        <v>2030</v>
       </c>
       <c r="I30" s="45" t="s">
-        <v>2048</v>
+        <v>2029</v>
       </c>
       <c r="J30" s="45" t="s">
-        <v>2047</v>
+        <v>2028</v>
       </c>
       <c r="K30" s="45" t="s">
-        <v>2669</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="28">
       <c r="A31" s="45" t="s">
-        <v>2046</v>
+        <v>2027</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>2045</v>
+        <v>2026</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>2044</v>
+        <v>2025</v>
       </c>
       <c r="D31" s="45" t="s">
-        <v>2043</v>
+        <v>2024</v>
       </c>
       <c r="E31" s="45" t="s">
-        <v>2042</v>
+        <v>2023</v>
       </c>
       <c r="F31" s="45" t="s">
-        <v>2041</v>
+        <v>2022</v>
       </c>
       <c r="G31" s="45" t="s">
-        <v>2040</v>
+        <v>2021</v>
       </c>
       <c r="H31" s="45" t="s">
-        <v>2039</v>
+        <v>2020</v>
       </c>
       <c r="I31" s="45" t="s">
-        <v>2038</v>
+        <v>2019</v>
       </c>
       <c r="J31" s="45" t="s">
-        <v>2037</v>
+        <v>2018</v>
       </c>
       <c r="K31" s="45" t="s">
-        <v>2670</v>
+        <v>2598</v>
       </c>
     </row>
   </sheetData>
@@ -30834,7 +31520,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18">
       <c r="A1" s="77" t="s">
-        <v>2177</v>
+        <v>2158</v>
       </c>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -30846,35 +31532,35 @@
     </row>
     <row r="3" spans="1:3" ht="15">
       <c r="A3" s="76" t="s">
-        <v>2176</v>
+        <v>2157</v>
       </c>
       <c r="B3" s="76"/>
       <c r="C3" s="76"/>
     </row>
     <row r="4" spans="1:3" ht="15">
       <c r="A4" s="76" t="s">
-        <v>2175</v>
+        <v>2156</v>
       </c>
       <c r="B4" s="76"/>
       <c r="C4" s="76"/>
     </row>
     <row r="5" spans="1:3" ht="15">
       <c r="A5" s="76" t="s">
-        <v>2174</v>
+        <v>2155</v>
       </c>
       <c r="B5" s="76"/>
       <c r="C5" s="76"/>
     </row>
     <row r="6" spans="1:3" ht="15">
       <c r="A6" s="76" t="s">
-        <v>2032</v>
+        <v>2013</v>
       </c>
       <c r="B6" s="76"/>
       <c r="C6" s="76"/>
     </row>
     <row r="7" spans="1:3" ht="30">
       <c r="A7" s="76" t="s">
-        <v>2173</v>
+        <v>2154</v>
       </c>
       <c r="B7" s="76"/>
       <c r="C7" s="76"/>
@@ -30891,7 +31577,7 @@
     </row>
     <row r="10" spans="1:3" ht="18">
       <c r="A10" s="77" t="s">
-        <v>2172</v>
+        <v>2153</v>
       </c>
       <c r="B10" s="76"/>
       <c r="C10" s="76"/>
@@ -30903,46 +31589,46 @@
     </row>
     <row r="12" spans="1:3" ht="18">
       <c r="A12" s="52" t="s">
-        <v>1960</v>
+        <v>1941</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>1987</v>
+        <v>1968</v>
       </c>
       <c r="C12" s="76"/>
     </row>
     <row r="13" spans="1:3" ht="28">
       <c r="A13" s="45" t="s">
-        <v>2171</v>
+        <v>2152</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>2170</v>
+        <v>2151</v>
       </c>
       <c r="C13" s="76"/>
     </row>
     <row r="14" spans="1:3" ht="28">
       <c r="A14" s="45" t="s">
-        <v>2169</v>
+        <v>2150</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>2168</v>
+        <v>2149</v>
       </c>
       <c r="C14" s="76"/>
     </row>
     <row r="15" spans="1:3" ht="28">
       <c r="A15" s="45" t="s">
-        <v>2167</v>
+        <v>2148</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>2166</v>
+        <v>2147</v>
       </c>
       <c r="C15" s="76"/>
     </row>
     <row r="16" spans="1:3" ht="28">
       <c r="A16" s="45" t="s">
-        <v>2165</v>
+        <v>2146</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>2164</v>
+        <v>2145</v>
       </c>
       <c r="C16" s="76"/>
     </row>
@@ -30958,7 +31644,7 @@
     </row>
     <row r="19" spans="1:3" ht="18">
       <c r="A19" s="77" t="s">
-        <v>2163</v>
+        <v>2144</v>
       </c>
       <c r="B19" s="76"/>
       <c r="C19" s="76"/>
@@ -30970,10 +31656,10 @@
     </row>
     <row r="21" spans="1:3" ht="18">
       <c r="A21" s="52" t="s">
-        <v>2162</v>
+        <v>2143</v>
       </c>
       <c r="B21" s="52" t="s">
-        <v>2161</v>
+        <v>2142</v>
       </c>
       <c r="C21" s="52" t="s">
         <v>34</v>
@@ -30981,24 +31667,24 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="45" t="s">
-        <v>2160</v>
+        <v>2141</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>2159</v>
+        <v>2140</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>2158</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="45" t="s">
-        <v>2157</v>
+        <v>2138</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>2156</v>
+        <v>2137</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>2155</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -31006,10 +31692,10 @@
         <v>564</v>
       </c>
       <c r="B24" s="45" t="s">
-        <v>2154</v>
+        <v>2135</v>
       </c>
       <c r="C24" s="45" t="s">
-        <v>2153</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -31017,21 +31703,21 @@
         <v>653</v>
       </c>
       <c r="B25" s="45" t="s">
-        <v>2152</v>
+        <v>2133</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>2151</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="45" t="s">
-        <v>2150</v>
+        <v>2131</v>
       </c>
       <c r="B26" s="45" t="s">
-        <v>2149</v>
+        <v>2130</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>2148</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -31039,10 +31725,10 @@
         <v>536</v>
       </c>
       <c r="B27" s="45" t="s">
-        <v>2147</v>
+        <v>2128</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>2146</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -31050,10 +31736,10 @@
         <v>539</v>
       </c>
       <c r="B28" s="45" t="s">
-        <v>2145</v>
+        <v>2126</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>2144</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -31061,10 +31747,10 @@
         <v>545</v>
       </c>
       <c r="B29" s="45" t="s">
-        <v>2143</v>
+        <v>2124</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>2142</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -31072,10 +31758,10 @@
         <v>548</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>2141</v>
+        <v>2122</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>2140</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -31083,10 +31769,10 @@
         <v>577</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>2139</v>
+        <v>2120</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>2138</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -31094,10 +31780,10 @@
         <v>619</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>2653</v>
+        <v>2581</v>
       </c>
       <c r="C32" s="45" t="s">
-        <v>2654</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -31107,7 +31793,7 @@
     </row>
     <row r="34" spans="1:3" ht="18">
       <c r="A34" s="77" t="s">
-        <v>2137</v>
+        <v>2118</v>
       </c>
       <c r="B34" s="76"/>
       <c r="C34" s="76"/>
@@ -31119,10 +31805,10 @@
     </row>
     <row r="36" spans="1:3" ht="18">
       <c r="A36" s="52" t="s">
-        <v>2136</v>
+        <v>2117</v>
       </c>
       <c r="B36" s="52" t="s">
-        <v>2135</v>
+        <v>2116</v>
       </c>
       <c r="C36" s="52" t="s">
         <v>4</v>
@@ -31130,13 +31816,13 @@
     </row>
     <row r="37" spans="1:3" ht="42">
       <c r="A37" s="45" t="s">
-        <v>2134</v>
+        <v>2115</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>2655</v>
+        <v>2583</v>
       </c>
       <c r="C37" s="45" t="s">
-        <v>2656</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="28">
@@ -31144,54 +31830,54 @@
         <v>41</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>2133</v>
+        <v>2114</v>
       </c>
       <c r="C38" s="45" t="s">
-        <v>2132</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="45" t="s">
-        <v>2131</v>
+        <v>2112</v>
       </c>
       <c r="B39" s="45" t="s">
-        <v>2130</v>
+        <v>2111</v>
       </c>
       <c r="C39" s="45" t="s">
-        <v>2129</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="28">
       <c r="A40" s="45" t="s">
-        <v>2128</v>
+        <v>2109</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>2127</v>
+        <v>2108</v>
       </c>
       <c r="C40" s="45" t="s">
-        <v>2126</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="28">
       <c r="A41" s="45" t="s">
-        <v>2125</v>
+        <v>2106</v>
       </c>
       <c r="B41" s="45" t="s">
-        <v>2124</v>
+        <v>2105</v>
       </c>
       <c r="C41" s="45" t="s">
-        <v>2123</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="28">
       <c r="A42" s="45" t="s">
-        <v>2122</v>
+        <v>2103</v>
       </c>
       <c r="B42" s="45" t="s">
-        <v>2121</v>
+        <v>2102</v>
       </c>
       <c r="C42" s="45" t="s">
-        <v>2120</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -31206,7 +31892,7 @@
     </row>
     <row r="45" spans="1:3" ht="18">
       <c r="A45" s="77" t="s">
-        <v>2119</v>
+        <v>2100</v>
       </c>
       <c r="B45" s="76"/>
       <c r="C45" s="76"/>
@@ -31218,14 +31904,14 @@
     </row>
     <row r="47" spans="1:3" ht="30">
       <c r="A47" s="76" t="s">
-        <v>2118</v>
+        <v>2099</v>
       </c>
       <c r="B47" s="76"/>
       <c r="C47" s="76"/>
     </row>
     <row r="48" spans="1:3" ht="15">
       <c r="A48" s="76" t="s">
-        <v>2117</v>
+        <v>2098</v>
       </c>
       <c r="B48" s="76"/>
       <c r="C48" s="76"/>
@@ -31253,7 +31939,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18">
       <c r="A1" s="98" t="s">
-        <v>2216</v>
+        <v>2197</v>
       </c>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -31265,35 +31951,35 @@
     </row>
     <row r="3" spans="1:3" ht="15">
       <c r="A3" s="76" t="s">
-        <v>2215</v>
+        <v>2196</v>
       </c>
       <c r="B3" s="76"/>
       <c r="C3" s="76"/>
     </row>
     <row r="4" spans="1:3" ht="15">
       <c r="A4" s="76" t="s">
-        <v>2214</v>
+        <v>2195</v>
       </c>
       <c r="B4" s="76"/>
       <c r="C4" s="76"/>
     </row>
     <row r="5" spans="1:3" ht="15">
       <c r="A5" s="76" t="s">
-        <v>2174</v>
+        <v>2155</v>
       </c>
       <c r="B5" s="76"/>
       <c r="C5" s="76"/>
     </row>
     <row r="6" spans="1:3" ht="15">
       <c r="A6" s="76" t="s">
-        <v>2032</v>
+        <v>2013</v>
       </c>
       <c r="B6" s="76"/>
       <c r="C6" s="76"/>
     </row>
     <row r="7" spans="1:3" ht="30">
       <c r="A7" s="76" t="s">
-        <v>2213</v>
+        <v>2194</v>
       </c>
       <c r="B7" s="76"/>
       <c r="C7" s="76"/>
@@ -31315,7 +32001,7 @@
     </row>
     <row r="11" spans="1:3" ht="18">
       <c r="A11" s="99" t="s">
-        <v>2209</v>
+        <v>2190</v>
       </c>
       <c r="B11" s="45"/>
       <c r="C11" s="45"/>
@@ -31327,55 +32013,55 @@
     </row>
     <row r="13" spans="1:3" ht="18">
       <c r="A13" s="52" t="s">
-        <v>1960</v>
+        <v>1941</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>2208</v>
+        <v>2189</v>
       </c>
       <c r="C13" s="45"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="45" t="s">
-        <v>1988</v>
+        <v>1969</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>2207</v>
+        <v>2188</v>
       </c>
       <c r="C14" s="45"/>
     </row>
     <row r="15" spans="1:3" ht="28">
       <c r="A15" s="45" t="s">
-        <v>2206</v>
+        <v>2187</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>2205</v>
+        <v>2186</v>
       </c>
       <c r="C15" s="45"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="45" t="s">
-        <v>2204</v>
+        <v>2185</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>2203</v>
+        <v>2184</v>
       </c>
       <c r="C16" s="45"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="45" t="s">
-        <v>2202</v>
+        <v>2183</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>2201</v>
+        <v>2182</v>
       </c>
       <c r="C17" s="45"/>
     </row>
     <row r="18" spans="1:3" ht="28">
       <c r="A18" s="45" t="s">
-        <v>2200</v>
+        <v>2181</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>2199</v>
+        <v>2180</v>
       </c>
       <c r="C18" s="45"/>
     </row>
@@ -31391,7 +32077,7 @@
     </row>
     <row r="21" spans="1:3" ht="18">
       <c r="A21" s="97" t="s">
-        <v>2638</v>
+        <v>2566</v>
       </c>
       <c r="B21" s="45"/>
       <c r="C21" s="45"/>
@@ -31403,43 +32089,43 @@
     </row>
     <row r="23" spans="1:3" ht="18">
       <c r="A23" s="52" t="s">
-        <v>2185</v>
+        <v>2166</v>
       </c>
       <c r="B23" s="52" t="s">
-        <v>2184</v>
+        <v>2165</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>2198</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="45" t="s">
-        <v>2197</v>
+        <v>2178</v>
       </c>
       <c r="B24" s="45" t="s">
-        <v>2196</v>
+        <v>2177</v>
       </c>
       <c r="C24" s="45" t="s">
-        <v>2195</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="45" t="s">
-        <v>2194</v>
+        <v>2175</v>
       </c>
       <c r="B25" s="45" t="s">
-        <v>2193</v>
+        <v>2174</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>2192</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="45" t="s">
-        <v>2191</v>
+        <v>2172</v>
       </c>
       <c r="B26" s="45" t="s">
-        <v>2190</v>
+        <v>2171</v>
       </c>
       <c r="C26" s="45" t="s">
         <v>43</v>
@@ -31447,13 +32133,13 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="45" t="s">
-        <v>2189</v>
+        <v>2170</v>
       </c>
       <c r="B27" s="45" t="s">
-        <v>2188</v>
+        <v>2169</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>2187</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -31468,7 +32154,7 @@
     </row>
     <row r="30" spans="1:3" ht="18">
       <c r="A30" s="97" t="s">
-        <v>2639</v>
+        <v>2567</v>
       </c>
       <c r="B30" s="45"/>
       <c r="C30" s="45"/>
@@ -31480,7 +32166,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="45" t="s">
-        <v>2640</v>
+        <v>2568</v>
       </c>
       <c r="B32" s="45"/>
       <c r="C32" s="45"/>
@@ -31492,10 +32178,10 @@
     </row>
     <row r="34" spans="1:3" ht="18">
       <c r="A34" s="52" t="s">
-        <v>2641</v>
+        <v>2569</v>
       </c>
       <c r="B34" s="52" t="s">
-        <v>2184</v>
+        <v>2165</v>
       </c>
       <c r="C34" s="52" t="s">
         <v>34</v>
@@ -31503,13 +32189,13 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="45" t="s">
-        <v>2186</v>
+        <v>2167</v>
       </c>
       <c r="B35" s="45" t="s">
-        <v>2642</v>
+        <v>2570</v>
       </c>
       <c r="C35" s="45" t="s">
-        <v>2643</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -31517,10 +32203,10 @@
         <v>1137</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>2644</v>
+        <v>2572</v>
       </c>
       <c r="C36" s="45" t="s">
-        <v>2645</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -31528,10 +32214,10 @@
         <v>1129</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>2646</v>
+        <v>2574</v>
       </c>
       <c r="C37" s="45" t="s">
-        <v>2647</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -31546,7 +32232,7 @@
     </row>
     <row r="40" spans="1:3" ht="18">
       <c r="A40" s="97" t="s">
-        <v>2648</v>
+        <v>2576</v>
       </c>
       <c r="B40" s="45"/>
       <c r="C40" s="45"/>
@@ -31558,51 +32244,51 @@
     </row>
     <row r="42" spans="1:3" ht="18">
       <c r="A42" s="52" t="s">
-        <v>2649</v>
+        <v>2577</v>
       </c>
       <c r="B42" s="52" t="s">
-        <v>2184</v>
+        <v>2165</v>
       </c>
       <c r="C42" s="52" t="s">
-        <v>2650</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="45" t="s">
-        <v>2183</v>
+        <v>2164</v>
       </c>
       <c r="B43" s="45" t="s">
-        <v>2182</v>
+        <v>2163</v>
       </c>
       <c r="C43" s="45" t="s">
-        <v>2651</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="45" t="s">
-        <v>2181</v>
+        <v>2162</v>
       </c>
       <c r="B44" s="45" t="s">
-        <v>2180</v>
+        <v>2161</v>
       </c>
       <c r="C44" s="45" t="s">
-        <v>2651</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="45" t="s">
-        <v>2179</v>
+        <v>2160</v>
       </c>
       <c r="B45" s="45" t="s">
-        <v>2178</v>
+        <v>2159</v>
       </c>
       <c r="C45" s="45" t="s">
-        <v>2652</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="18">
       <c r="A50" s="98" t="s">
-        <v>2212</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -31610,12 +32296,12 @@
     </row>
     <row r="52" spans="1:1" ht="28">
       <c r="A52" s="45" t="s">
-        <v>2211</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="53" spans="1:1" ht="28">
       <c r="A53" s="45" t="s">
-        <v>2210</v>
+        <v>2191</v>
       </c>
     </row>
   </sheetData>
@@ -31684,7 +32370,7 @@
         <v>8</v>
       </c>
       <c r="I5" s="95" t="s">
-        <v>2635</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14">
@@ -31705,7 +32391,7 @@
       <c r="G6" s="45"/>
       <c r="H6" s="45"/>
       <c r="I6" s="45" t="s">
-        <v>2615</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="28">
@@ -31726,7 +32412,7 @@
       <c r="G7" s="45"/>
       <c r="H7" s="45"/>
       <c r="I7" s="45" t="s">
-        <v>2615</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14">
@@ -31747,7 +32433,7 @@
       <c r="G8" s="45"/>
       <c r="H8" s="45"/>
       <c r="I8" s="45" t="s">
-        <v>2615</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14">
@@ -31768,7 +32454,7 @@
       <c r="G9" s="45"/>
       <c r="H9" s="45"/>
       <c r="I9" s="45" t="s">
-        <v>2615</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="28">
@@ -31789,7 +32475,7 @@
       <c r="G10" s="45"/>
       <c r="H10" s="45"/>
       <c r="I10" s="45" t="s">
-        <v>2615</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="28">
@@ -31810,7 +32496,7 @@
       <c r="G11" s="45"/>
       <c r="H11" s="45"/>
       <c r="I11" s="45" t="s">
-        <v>2615</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="28">
@@ -31831,7 +32517,7 @@
       <c r="G12" s="45"/>
       <c r="H12" s="45"/>
       <c r="I12" s="45" t="s">
-        <v>2616</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14">
@@ -31852,7 +32538,7 @@
       <c r="G13" s="45"/>
       <c r="H13" s="45"/>
       <c r="I13" s="45" t="s">
-        <v>2616</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="28">
@@ -31873,7 +32559,7 @@
       <c r="G14" s="45"/>
       <c r="H14" s="45"/>
       <c r="I14" s="45" t="s">
-        <v>2616</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="28">
@@ -31894,7 +32580,7 @@
       <c r="G15" s="45"/>
       <c r="H15" s="45"/>
       <c r="I15" s="45" t="s">
-        <v>2616</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="21.75" customHeight="1">
@@ -31915,7 +32601,7 @@
       <c r="G16" s="45"/>
       <c r="H16" s="45"/>
       <c r="I16" s="45" t="s">
-        <v>2616</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="21.75" customHeight="1">
@@ -31936,7 +32622,7 @@
       <c r="G17" s="45"/>
       <c r="H17" s="45"/>
       <c r="I17" s="45" t="s">
-        <v>2616</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="14">
@@ -31957,7 +32643,7 @@
       <c r="G18" s="45"/>
       <c r="H18" s="45"/>
       <c r="I18" s="45" t="s">
-        <v>2616</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="14">
@@ -31978,7 +32664,7 @@
       <c r="G19" s="45"/>
       <c r="H19" s="45"/>
       <c r="I19" s="45" t="s">
-        <v>2616</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="28">
@@ -31999,7 +32685,7 @@
       <c r="G20" s="45"/>
       <c r="H20" s="45"/>
       <c r="I20" s="45" t="s">
-        <v>2616</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="14">
@@ -32020,7 +32706,7 @@
       <c r="G21" s="45"/>
       <c r="H21" s="45"/>
       <c r="I21" s="45" t="s">
-        <v>2616</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="28">
@@ -32041,7 +32727,7 @@
       <c r="G22" s="45"/>
       <c r="H22" s="45"/>
       <c r="I22" s="45" t="s">
-        <v>2617</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="14">
@@ -32062,7 +32748,7 @@
       <c r="G23" s="45"/>
       <c r="H23" s="45"/>
       <c r="I23" s="45" t="s">
-        <v>2617</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="14">
@@ -32083,7 +32769,7 @@
       <c r="G24" s="45"/>
       <c r="H24" s="45"/>
       <c r="I24" s="45" t="s">
-        <v>2617</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="14">
@@ -32104,7 +32790,7 @@
       <c r="G25" s="45"/>
       <c r="H25" s="45"/>
       <c r="I25" s="45" t="s">
-        <v>2617</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1">
@@ -32124,7 +32810,7 @@
       <c r="G26" s="45"/>
       <c r="H26" s="45"/>
       <c r="I26" s="45" t="s">
-        <v>2617</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1">
@@ -32144,7 +32830,7 @@
       <c r="G27" s="45"/>
       <c r="H27" s="45"/>
       <c r="I27" s="45" t="s">
-        <v>2617</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1">
@@ -32164,7 +32850,7 @@
       <c r="G28" s="45"/>
       <c r="H28" s="45"/>
       <c r="I28" s="45" t="s">
-        <v>2617</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1">
@@ -32184,7 +32870,7 @@
       <c r="G29" s="45"/>
       <c r="H29" s="45"/>
       <c r="I29" s="45" t="s">
-        <v>2617</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" customHeight="1">
@@ -32204,7 +32890,7 @@
       <c r="G30" s="45"/>
       <c r="H30" s="45"/>
       <c r="I30" s="45" t="s">
-        <v>2617</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1">
@@ -32224,7 +32910,7 @@
       <c r="G31" s="45"/>
       <c r="H31" s="45"/>
       <c r="I31" s="45" t="s">
-        <v>2618</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1">
@@ -32244,7 +32930,7 @@
       <c r="G32" s="45"/>
       <c r="H32" s="45"/>
       <c r="I32" s="45" t="s">
-        <v>2618</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="15.75" customHeight="1">
@@ -32264,7 +32950,7 @@
       <c r="G33" s="45"/>
       <c r="H33" s="45"/>
       <c r="I33" s="45" t="s">
-        <v>2618</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="15.75" customHeight="1">
@@ -32284,7 +32970,7 @@
       <c r="G34" s="45"/>
       <c r="H34" s="45"/>
       <c r="I34" s="45" t="s">
-        <v>2618</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="15.75" customHeight="1">
@@ -32304,7 +32990,7 @@
       <c r="G35" s="45"/>
       <c r="H35" s="45"/>
       <c r="I35" s="45" t="s">
-        <v>2618</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="15.75" customHeight="1">
@@ -32324,7 +33010,7 @@
       <c r="G36" s="45"/>
       <c r="H36" s="45"/>
       <c r="I36" s="45" t="s">
-        <v>2618</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="15.75" customHeight="1">
@@ -32344,7 +33030,7 @@
       <c r="G37" s="45"/>
       <c r="H37" s="45"/>
       <c r="I37" s="45" t="s">
-        <v>2618</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="15.75" customHeight="1">
@@ -32364,7 +33050,7 @@
       <c r="G38" s="45"/>
       <c r="H38" s="45"/>
       <c r="I38" s="45" t="s">
-        <v>2618</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="15.75" customHeight="1">
@@ -32384,7 +33070,7 @@
       <c r="G39" s="45"/>
       <c r="H39" s="45"/>
       <c r="I39" s="45" t="s">
-        <v>2619</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15.75" customHeight="1">
@@ -32404,7 +33090,7 @@
       <c r="G40" s="45"/>
       <c r="H40" s="45"/>
       <c r="I40" s="45" t="s">
-        <v>2619</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="15.75" customHeight="1">
@@ -32424,7 +33110,7 @@
       <c r="G41" s="45"/>
       <c r="H41" s="45"/>
       <c r="I41" s="45" t="s">
-        <v>2619</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="15.75" customHeight="1">
@@ -32444,7 +33130,7 @@
       <c r="G42" s="45"/>
       <c r="H42" s="45"/>
       <c r="I42" s="45" t="s">
-        <v>2620</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="15.75" customHeight="1">
@@ -32464,7 +33150,7 @@
       <c r="G43" s="45"/>
       <c r="H43" s="45"/>
       <c r="I43" s="45" t="s">
-        <v>2620</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="44" spans="2:9" ht="15.75" customHeight="1">
@@ -32484,7 +33170,7 @@
       <c r="G44" s="45"/>
       <c r="H44" s="45"/>
       <c r="I44" s="45" t="s">
-        <v>2620</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="15.75" customHeight="1">
@@ -32504,7 +33190,7 @@
       <c r="G45" s="45"/>
       <c r="H45" s="45"/>
       <c r="I45" s="45" t="s">
-        <v>2620</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="46" spans="2:9" ht="15.75" customHeight="1">
@@ -32524,7 +33210,7 @@
       <c r="G46" s="45"/>
       <c r="H46" s="45"/>
       <c r="I46" s="45" t="s">
-        <v>2620</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="47" spans="2:9" ht="15.75" customHeight="1">
@@ -32544,7 +33230,7 @@
       <c r="G47" s="45"/>
       <c r="H47" s="45"/>
       <c r="I47" s="45" t="s">
-        <v>2620</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="48" spans="2:9" ht="15.75" customHeight="1">
@@ -32564,7 +33250,7 @@
       <c r="G48" s="45"/>
       <c r="H48" s="45"/>
       <c r="I48" s="45" t="s">
-        <v>2620</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="49" spans="2:9" ht="15.75" customHeight="1">
@@ -32584,7 +33270,7 @@
       <c r="G49" s="45"/>
       <c r="H49" s="45"/>
       <c r="I49" s="45" t="s">
-        <v>2620</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="50" spans="2:9" ht="15.75" customHeight="1">
@@ -32604,7 +33290,7 @@
       <c r="G50" s="45"/>
       <c r="H50" s="45"/>
       <c r="I50" s="45" t="s">
-        <v>2620</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="51" spans="2:9" ht="15.75" customHeight="1">
@@ -32615,7 +33301,7 @@
         <v>206</v>
       </c>
       <c r="D51" s="45" t="s">
-        <v>2621</v>
+        <v>2549</v>
       </c>
       <c r="E51" s="45" t="s">
         <v>12</v>
@@ -32624,7 +33310,7 @@
       <c r="G51" s="45"/>
       <c r="H51" s="45"/>
       <c r="I51" s="45" t="s">
-        <v>2620</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="52" spans="2:9" ht="15.75" customHeight="1">
@@ -32644,7 +33330,7 @@
       <c r="G52" s="45"/>
       <c r="H52" s="45"/>
       <c r="I52" s="45" t="s">
-        <v>2620</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="53" spans="2:9" ht="15.75" customHeight="1">
@@ -32664,7 +33350,7 @@
       <c r="G53" s="45"/>
       <c r="H53" s="45"/>
       <c r="I53" s="45" t="s">
-        <v>2620</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="54" spans="2:9" ht="15.75" customHeight="1">
@@ -32684,7 +33370,7 @@
       <c r="G54" s="45"/>
       <c r="H54" s="45"/>
       <c r="I54" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="55" spans="2:9" ht="15.75" customHeight="1">
@@ -32704,7 +33390,7 @@
       <c r="G55" s="45"/>
       <c r="H55" s="45"/>
       <c r="I55" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="56" spans="2:9" ht="15.75" customHeight="1">
@@ -32724,7 +33410,7 @@
       <c r="G56" s="45"/>
       <c r="H56" s="45"/>
       <c r="I56" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="15.75" customHeight="1">
@@ -32746,7 +33432,7 @@
         <v>225</v>
       </c>
       <c r="I57" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="58" spans="2:9" ht="15.75" customHeight="1">
@@ -32768,7 +33454,7 @@
         <v>225</v>
       </c>
       <c r="I58" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="59" spans="2:9" ht="15.75" customHeight="1">
@@ -32776,10 +33462,10 @@
         <v>229</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>2577</v>
+        <v>2505</v>
       </c>
       <c r="D59" s="45" t="s">
-        <v>2623</v>
+        <v>2551</v>
       </c>
       <c r="E59" s="45" t="s">
         <v>10</v>
@@ -32790,7 +33476,7 @@
         <v>225</v>
       </c>
       <c r="I59" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="60" spans="2:9" ht="15.75" customHeight="1">
@@ -32798,10 +33484,10 @@
         <v>230</v>
       </c>
       <c r="C60" s="45" t="s">
-        <v>2580</v>
+        <v>2508</v>
       </c>
       <c r="D60" s="45" t="s">
-        <v>2624</v>
+        <v>2552</v>
       </c>
       <c r="E60" s="45" t="s">
         <v>10</v>
@@ -32812,7 +33498,7 @@
         <v>225</v>
       </c>
       <c r="I60" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="61" spans="2:9" ht="15.75" customHeight="1">
@@ -32820,10 +33506,10 @@
         <v>231</v>
       </c>
       <c r="C61" s="45" t="s">
-        <v>2583</v>
+        <v>2511</v>
       </c>
       <c r="D61" s="45" t="s">
-        <v>2625</v>
+        <v>2553</v>
       </c>
       <c r="E61" s="45" t="s">
         <v>10</v>
@@ -32834,7 +33520,7 @@
         <v>225</v>
       </c>
       <c r="I61" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="62" spans="2:9" ht="15.75" customHeight="1">
@@ -32856,7 +33542,7 @@
         <v>235</v>
       </c>
       <c r="I62" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="63" spans="2:9" ht="15.75" customHeight="1">
@@ -32878,7 +33564,7 @@
         <v>235</v>
       </c>
       <c r="I63" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="64" spans="2:9" ht="15.75" customHeight="1">
@@ -32900,7 +33586,7 @@
         <v>235</v>
       </c>
       <c r="I64" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="65" spans="2:9" ht="15.75" customHeight="1">
@@ -32922,7 +33608,7 @@
         <v>235</v>
       </c>
       <c r="I65" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="66" spans="2:9" ht="15.75" customHeight="1">
@@ -32944,7 +33630,7 @@
         <v>235</v>
       </c>
       <c r="I66" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="67" spans="2:9" ht="15.75" customHeight="1">
@@ -32966,7 +33652,7 @@
         <v>235</v>
       </c>
       <c r="I67" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="68" spans="2:9" ht="15.75" customHeight="1">
@@ -32988,7 +33674,7 @@
         <v>235</v>
       </c>
       <c r="I68" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="69" spans="2:9" ht="15.75" customHeight="1">
@@ -33010,7 +33696,7 @@
         <v>235</v>
       </c>
       <c r="I69" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="15.75" customHeight="1">
@@ -33032,7 +33718,7 @@
         <v>235</v>
       </c>
       <c r="I70" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="71" spans="2:9" ht="15.75" customHeight="1">
@@ -33043,7 +33729,7 @@
         <v>261</v>
       </c>
       <c r="D71" s="45" t="s">
-        <v>2626</v>
+        <v>2554</v>
       </c>
       <c r="E71" s="45" t="s">
         <v>10</v>
@@ -33054,7 +33740,7 @@
         <v>235</v>
       </c>
       <c r="I71" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="72" spans="2:9" ht="15.75" customHeight="1">
@@ -33076,7 +33762,7 @@
         <v>265</v>
       </c>
       <c r="I72" s="45" t="s">
-        <v>2627</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="73" spans="2:9" ht="15.75" customHeight="1">
@@ -33098,7 +33784,7 @@
         <v>265</v>
       </c>
       <c r="I73" s="45" t="s">
-        <v>2627</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="74" spans="2:9" ht="15.75" customHeight="1">
@@ -33120,7 +33806,7 @@
         <v>265</v>
       </c>
       <c r="I74" s="45" t="s">
-        <v>2627</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="75" spans="2:9" ht="15.75" customHeight="1">
@@ -33142,7 +33828,7 @@
         <v>265</v>
       </c>
       <c r="I75" s="45" t="s">
-        <v>2627</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="76" spans="2:9" ht="15.75" customHeight="1">
@@ -33164,7 +33850,7 @@
         <v>265</v>
       </c>
       <c r="I76" s="45" t="s">
-        <v>2627</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="77" spans="2:9" ht="15.75" customHeight="1">
@@ -33186,7 +33872,7 @@
         <v>265</v>
       </c>
       <c r="I77" s="45" t="s">
-        <v>2627</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="78" spans="2:9" ht="15.75" customHeight="1">
@@ -33208,7 +33894,7 @@
         <v>265</v>
       </c>
       <c r="I78" s="45" t="s">
-        <v>2627</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="79" spans="2:9" ht="15.75" customHeight="1">
@@ -33230,7 +33916,7 @@
         <v>265</v>
       </c>
       <c r="I79" s="45" t="s">
-        <v>2627</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="80" spans="2:9" ht="15.75" customHeight="1">
@@ -33252,7 +33938,7 @@
         <v>290</v>
       </c>
       <c r="I80" s="45" t="s">
-        <v>2628</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="15.75" customHeight="1">
@@ -33274,7 +33960,7 @@
         <v>290</v>
       </c>
       <c r="I81" s="45" t="s">
-        <v>2628</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="82" spans="2:9" ht="15.75" customHeight="1">
@@ -33296,7 +33982,7 @@
         <v>290</v>
       </c>
       <c r="I82" s="45" t="s">
-        <v>2628</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="83" spans="2:9" ht="15.75" customHeight="1">
@@ -33318,7 +34004,7 @@
         <v>290</v>
       </c>
       <c r="I83" s="45" t="s">
-        <v>2628</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="15.75" customHeight="1">
@@ -33340,7 +34026,7 @@
         <v>290</v>
       </c>
       <c r="I84" s="45" t="s">
-        <v>2628</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="85" spans="2:9" ht="15.75" customHeight="1">
@@ -33362,7 +34048,7 @@
         <v>290</v>
       </c>
       <c r="I85" s="45" t="s">
-        <v>2628</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="86" spans="2:9" ht="15.75" customHeight="1">
@@ -33384,7 +34070,7 @@
         <v>290</v>
       </c>
       <c r="I86" s="45" t="s">
-        <v>2628</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="87" spans="2:9" ht="15.75" customHeight="1">
@@ -33406,7 +34092,7 @@
         <v>290</v>
       </c>
       <c r="I87" s="45" t="s">
-        <v>2628</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="88" spans="2:9" ht="15.75" customHeight="1">
@@ -33428,7 +34114,7 @@
         <v>315</v>
       </c>
       <c r="I88" s="45" t="s">
-        <v>2629</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="89" spans="2:9" ht="15.75" customHeight="1">
@@ -33450,7 +34136,7 @@
         <v>315</v>
       </c>
       <c r="I89" s="45" t="s">
-        <v>2629</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="90" spans="2:9" ht="15.75" customHeight="1">
@@ -33472,7 +34158,7 @@
         <v>315</v>
       </c>
       <c r="I90" s="45" t="s">
-        <v>2629</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="91" spans="2:9" ht="15.75" customHeight="1">
@@ -33494,7 +34180,7 @@
         <v>315</v>
       </c>
       <c r="I91" s="45" t="s">
-        <v>2629</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="92" spans="2:9" ht="15.75" customHeight="1">
@@ -33516,7 +34202,7 @@
         <v>315</v>
       </c>
       <c r="I92" s="45" t="s">
-        <v>2629</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="93" spans="2:9" ht="15.75" customHeight="1">
@@ -33538,7 +34224,7 @@
         <v>315</v>
       </c>
       <c r="I93" s="45" t="s">
-        <v>2629</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="94" spans="2:9" ht="15.75" customHeight="1">
@@ -33560,7 +34246,7 @@
         <v>315</v>
       </c>
       <c r="I94" s="45" t="s">
-        <v>2629</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="95" spans="2:9" ht="15.75" customHeight="1">
@@ -33582,7 +34268,7 @@
         <v>315</v>
       </c>
       <c r="I95" s="45" t="s">
-        <v>2629</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="96" spans="2:9" ht="15.75" customHeight="1">
@@ -33604,7 +34290,7 @@
         <v>315</v>
       </c>
       <c r="I96" s="45" t="s">
-        <v>2629</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="97" spans="2:9" ht="15.75" customHeight="1">
@@ -33626,7 +34312,7 @@
         <v>315</v>
       </c>
       <c r="I97" s="45" t="s">
-        <v>2629</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="98" spans="2:9" ht="15.75" customHeight="1">
@@ -33634,10 +34320,10 @@
         <v>343</v>
       </c>
       <c r="C98" s="45" t="s">
-        <v>2630</v>
+        <v>2558</v>
       </c>
       <c r="D98" s="45" t="s">
-        <v>2631</v>
+        <v>2559</v>
       </c>
       <c r="E98" s="45" t="s">
         <v>10</v>
@@ -33648,7 +34334,7 @@
         <v>315</v>
       </c>
       <c r="I98" s="45" t="s">
-        <v>2629</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="99" spans="2:9" ht="15.75" customHeight="1">
@@ -33670,7 +34356,7 @@
         <v>315</v>
       </c>
       <c r="I99" s="45" t="s">
-        <v>2629</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="100" spans="2:9" ht="15.75" customHeight="1">
@@ -33692,18 +34378,18 @@
         <v>315</v>
       </c>
       <c r="I100" s="45" t="s">
-        <v>2629</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="101" spans="2:9" ht="15.75" customHeight="1">
       <c r="B101" s="96" t="s">
-        <v>2636</v>
+        <v>2564</v>
       </c>
       <c r="C101" s="45" t="s">
         <v>393</v>
       </c>
       <c r="D101" s="45" t="s">
-        <v>2632</v>
+        <v>2560</v>
       </c>
       <c r="E101" s="45" t="s">
         <v>12</v>
@@ -33711,21 +34397,21 @@
       <c r="F101" s="45"/>
       <c r="G101" s="45"/>
       <c r="H101" s="45" t="s">
-        <v>2633</v>
+        <v>2561</v>
       </c>
       <c r="I101" s="45" t="s">
-        <v>2617</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="102" spans="2:9" ht="15.75" customHeight="1">
       <c r="B102" s="96" t="s">
-        <v>2637</v>
+        <v>2565</v>
       </c>
       <c r="C102" s="45" t="s">
         <v>394</v>
       </c>
       <c r="D102" s="45" t="s">
-        <v>2634</v>
+        <v>2562</v>
       </c>
       <c r="E102" s="45" t="s">
         <v>12</v>
@@ -33733,15 +34419,15 @@
       <c r="F102" s="45"/>
       <c r="G102" s="45"/>
       <c r="H102" s="45" t="s">
-        <v>2633</v>
+        <v>2561</v>
       </c>
       <c r="I102" s="45" t="s">
-        <v>2617</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="107" spans="2:9" ht="15.75" customHeight="1">
       <c r="B107" s="97" t="s">
-        <v>2705</v>
+        <v>2633</v>
       </c>
       <c r="C107" s="45"/>
     </row>
@@ -33751,90 +34437,90 @@
     </row>
     <row r="109" spans="2:9" ht="15.75" customHeight="1">
       <c r="B109" s="2" t="s">
-        <v>2635</v>
+        <v>2563</v>
       </c>
       <c r="C109" s="102" t="s">
-        <v>2716</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="110" spans="2:9" ht="15.75" customHeight="1">
       <c r="B110" s="45" t="s">
-        <v>2620</v>
+        <v>2548</v>
       </c>
       <c r="C110" s="45" t="s">
-        <v>2706</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="111" spans="2:9" ht="15.75" customHeight="1">
       <c r="B111" s="45" t="s">
-        <v>2615</v>
+        <v>2543</v>
       </c>
       <c r="C111" s="45" t="s">
-        <v>2707</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="112" spans="2:9" ht="15.75" customHeight="1">
       <c r="B112" s="45" t="s">
-        <v>2616</v>
+        <v>2544</v>
       </c>
       <c r="C112" s="45" t="s">
-        <v>2708</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="113" spans="2:3" ht="15.75" customHeight="1">
       <c r="B113" s="45" t="s">
-        <v>2617</v>
+        <v>2545</v>
       </c>
       <c r="C113" s="45" t="s">
-        <v>2709</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="114" spans="2:3" ht="15.75" customHeight="1">
       <c r="B114" s="45" t="s">
-        <v>2618</v>
+        <v>2546</v>
       </c>
       <c r="C114" s="45" t="s">
-        <v>2710</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="115" spans="2:3" ht="15.75" customHeight="1">
       <c r="B115" s="45" t="s">
-        <v>2619</v>
+        <v>2547</v>
       </c>
       <c r="C115" s="45" t="s">
-        <v>2711</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="116" spans="2:3" ht="15.75" customHeight="1">
       <c r="B116" s="45" t="s">
-        <v>2622</v>
+        <v>2550</v>
       </c>
       <c r="C116" s="45" t="s">
-        <v>2712</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="117" spans="2:3" ht="15.75" customHeight="1">
       <c r="B117" s="45" t="s">
-        <v>2627</v>
+        <v>2555</v>
       </c>
       <c r="C117" s="45" t="s">
-        <v>2713</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="118" spans="2:3" ht="15.75" customHeight="1">
       <c r="B118" s="45" t="s">
-        <v>2628</v>
+        <v>2556</v>
       </c>
       <c r="C118" s="45" t="s">
-        <v>2714</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="119" spans="2:3" ht="15.75" customHeight="1">
       <c r="B119" s="45" t="s">
-        <v>2629</v>
+        <v>2557</v>
       </c>
       <c r="C119" s="45" t="s">
-        <v>2715</v>
+        <v>2643</v>
       </c>
     </row>
   </sheetData>
@@ -34210,13 +34896,13 @@
         <v>414</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>2569</v>
+        <v>2497</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>415</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>2570</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
@@ -34405,16 +35091,16 @@
         <v>39</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>2571</v>
+        <v>2499</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>2572</v>
+        <v>2500</v>
       </c>
       <c r="E31" s="17" t="s">
         <v>424</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>2573</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1">
@@ -34423,16 +35109,16 @@
         <v>39</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>2574</v>
+        <v>2502</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>2575</v>
+        <v>2503</v>
       </c>
       <c r="E32" s="17" t="s">
         <v>424</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>2576</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" customHeight="1">
@@ -34657,16 +35343,16 @@
         <v>39</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>2577</v>
+        <v>2505</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>2578</v>
+        <v>2506</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>464</v>
       </c>
       <c r="F45" s="17" t="s">
-        <v>2579</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" customHeight="1">
@@ -34675,16 +35361,16 @@
         <v>39</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>2580</v>
+        <v>2508</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>2581</v>
+        <v>2509</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>464</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>2582</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" customHeight="1">
@@ -34693,16 +35379,16 @@
         <v>39</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>2583</v>
+        <v>2511</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>2584</v>
+        <v>2512</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>464</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>2585</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" customHeight="1">
@@ -34717,7 +35403,7 @@
         <v>475</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>2586</v>
+        <v>2514</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>476</v>
@@ -34735,7 +35421,7 @@
         <v>478</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>2586</v>
+        <v>2514</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>479</v>
@@ -34747,16 +35433,16 @@
         <v>39</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>2587</v>
+        <v>2515</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>2588</v>
+        <v>2516</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>2586</v>
+        <v>2514</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>2589</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" customHeight="1">
@@ -34771,7 +35457,7 @@
         <v>481</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>2586</v>
+        <v>2514</v>
       </c>
       <c r="F51" s="17" t="s">
         <v>482</v>
@@ -34789,7 +35475,7 @@
         <v>484</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>2590</v>
+        <v>2518</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>485</v>
@@ -34807,7 +35493,7 @@
         <v>486</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>2590</v>
+        <v>2518</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>487</v>
@@ -34825,7 +35511,7 @@
         <v>489</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>2590</v>
+        <v>2518</v>
       </c>
       <c r="F54" s="17" t="s">
         <v>490</v>
@@ -34843,7 +35529,7 @@
         <v>492</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>2590</v>
+        <v>2518</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>493</v>
@@ -34861,7 +35547,7 @@
         <v>495</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>2591</v>
+        <v>2519</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>496</v>
@@ -34879,7 +35565,7 @@
         <v>498</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>2591</v>
+        <v>2519</v>
       </c>
       <c r="F57" s="17" t="s">
         <v>499</v>
@@ -34897,7 +35583,7 @@
         <v>501</v>
       </c>
       <c r="E58" s="46" t="s">
-        <v>2611</v>
+        <v>2539</v>
       </c>
       <c r="F58" s="17" t="s">
         <v>502</v>
@@ -34915,7 +35601,7 @@
         <v>504</v>
       </c>
       <c r="E59" s="46" t="s">
-        <v>2611</v>
+        <v>2539</v>
       </c>
       <c r="F59" s="17" t="s">
         <v>505</v>
@@ -34933,7 +35619,7 @@
         <v>507</v>
       </c>
       <c r="E60" s="46" t="s">
-        <v>2611</v>
+        <v>2539</v>
       </c>
       <c r="F60" s="17" t="s">
         <v>508</v>
@@ -34951,7 +35637,7 @@
         <v>510</v>
       </c>
       <c r="E61" s="46" t="s">
-        <v>2611</v>
+        <v>2539</v>
       </c>
       <c r="F61" s="17" t="s">
         <v>511</v>
@@ -34969,7 +35655,7 @@
         <v>513</v>
       </c>
       <c r="E62" s="46" t="s">
-        <v>2611</v>
+        <v>2539</v>
       </c>
       <c r="F62" s="17" t="s">
         <v>514</v>
@@ -34987,7 +35673,7 @@
         <v>516</v>
       </c>
       <c r="E63" s="46" t="s">
-        <v>2612</v>
+        <v>2540</v>
       </c>
       <c r="F63" s="17" t="s">
         <v>517</v>
@@ -35005,7 +35691,7 @@
         <v>519</v>
       </c>
       <c r="E64" s="46" t="s">
-        <v>2612</v>
+        <v>2540</v>
       </c>
       <c r="F64" s="17" t="s">
         <v>520</v>
@@ -35023,7 +35709,7 @@
         <v>522</v>
       </c>
       <c r="E65" s="46" t="s">
-        <v>2613</v>
+        <v>2541</v>
       </c>
       <c r="F65" s="17" t="s">
         <v>523</v>
@@ -35041,7 +35727,7 @@
         <v>525</v>
       </c>
       <c r="E66" s="46" t="s">
-        <v>2613</v>
+        <v>2541</v>
       </c>
       <c r="F66" s="17" t="s">
         <v>526</v>
@@ -35059,7 +35745,7 @@
         <v>528</v>
       </c>
       <c r="E67" s="46" t="s">
-        <v>2613</v>
+        <v>2541</v>
       </c>
       <c r="F67" s="17" t="s">
         <v>529</v>
@@ -35071,16 +35757,16 @@
         <v>39</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>2592</v>
+        <v>2520</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>2593</v>
+        <v>2521</v>
       </c>
       <c r="E68" s="46" t="s">
-        <v>2612</v>
+        <v>2540</v>
       </c>
       <c r="F68" s="17" t="s">
-        <v>2594</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" customHeight="1">
@@ -35095,7 +35781,7 @@
         <v>531</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>2614</v>
+        <v>2542</v>
       </c>
       <c r="F69" s="17" t="s">
         <v>532</v>
@@ -35113,7 +35799,7 @@
         <v>534</v>
       </c>
       <c r="E70" s="46" t="s">
-        <v>2614</v>
+        <v>2542</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>535</v>
@@ -35125,13 +35811,13 @@
         <v>677</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>2595</v>
+        <v>2523</v>
       </c>
       <c r="D71" s="12" t="s">
         <v>678</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>2596</v>
+        <v>2524</v>
       </c>
       <c r="F71" s="13" t="s">
         <v>679</v>
@@ -35143,13 +35829,13 @@
         <v>677</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>2597</v>
+        <v>2525</v>
       </c>
       <c r="D72" s="12" t="s">
         <v>680</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>2598</v>
+        <v>2526</v>
       </c>
       <c r="F72" s="13" t="s">
         <v>681</v>
@@ -35161,16 +35847,16 @@
         <v>677</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>2599</v>
+        <v>2527</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>2600</v>
+        <v>2528</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>2601</v>
+        <v>2529</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>2602</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15.75" customHeight="1">
@@ -35179,16 +35865,16 @@
         <v>677</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>2603</v>
+        <v>2531</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>2604</v>
+        <v>2532</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>2605</v>
+        <v>2533</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>2606</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15.75" customHeight="1">
@@ -35197,16 +35883,16 @@
         <v>677</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>2607</v>
+        <v>2535</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>2608</v>
+        <v>2536</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>2609</v>
+        <v>2537</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>2610</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15.75" customHeight="1">
@@ -35272,10 +35958,10 @@
         <v>40</v>
       </c>
       <c r="B1" s="112" t="s">
-        <v>2703</v>
+        <v>2631</v>
       </c>
       <c r="C1" s="110" t="s">
-        <v>2704</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -35602,19 +36288,19 @@
         <v>611</v>
       </c>
       <c r="B35" s="91" t="s">
-        <v>2564</v>
+        <v>2492</v>
       </c>
       <c r="C35" s="93" t="s">
-        <v>2566</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1">
       <c r="A36" s="82"/>
       <c r="B36" s="92" t="s">
-        <v>2565</v>
+        <v>2493</v>
       </c>
       <c r="C36" s="94" t="s">
-        <v>2567</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1">
@@ -35632,7 +36318,7 @@
         <v>614</v>
       </c>
       <c r="C38" s="94" t="s">
-        <v>2568</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" customHeight="1">
@@ -43496,7 +44182,7 @@
         <v>773</v>
       </c>
       <c r="G148" s="61" t="s">
-        <v>2557</v>
+        <v>2485</v>
       </c>
       <c r="H148" s="45"/>
       <c r="I148" s="45" t="s">
@@ -44265,7 +44951,7 @@
         <v>61</v>
       </c>
       <c r="G163" s="55" t="s">
-        <v>2560</v>
+        <v>2488</v>
       </c>
       <c r="H163" s="45"/>
       <c r="I163" s="45" t="s">
@@ -44316,7 +45002,7 @@
         <v>745</v>
       </c>
       <c r="G164" s="61" t="s">
-        <v>2563</v>
+        <v>2491</v>
       </c>
       <c r="H164" s="45"/>
       <c r="I164" s="45" t="s">
@@ -47529,10 +48215,10 @@
         <v>1582</v>
       </c>
       <c r="F226" s="57" t="s">
-        <v>2217</v>
+        <v>2198</v>
       </c>
       <c r="G226" s="61" t="s">
-        <v>2562</v>
+        <v>2490</v>
       </c>
       <c r="H226" s="45"/>
       <c r="I226" s="45"/>
